--- a/kobo/ais.xlsx
+++ b/kobo/ais.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J52"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -548,7 +548,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Esta inspección registra ubicación, características y fotos de la edificación para priorizar la evaluación estructural post-sismo. Los datos se tratan bajo la Ley 1581 de 2012.</t>
+          <t>AVISO DE PRIVACIDAD — Esta inspección registra ubicación, características y fotografías de la edificación (solo exteriores y elementos estructurales, no personas ni interiores habitados salvo lo estrictamente necesario) para priorizar la evaluación estructural post-sismo. Tratamiento según la Ley 1581 de 2012; política completa disponible con la entidad coordinadora. La clasificación resultante es un insumo de priorización: la habilitación definitiva es competencia de las autoridades.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -557,12 +557,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one tipos_inspeccion</t>
+          <t>select_one confirmaciones</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>tipo_inspeccion</t>
+          <t>aviso_comunicado</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -576,21 +576,25 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Tipo de inspección</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>¿Informaste al ocupante o responsable del inmueble el propósito de la inspección y el aviso de privacidad?</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Si no hay nadie presente, marca «No aplica (inmueble desocupado o sin acceso)»</t>
+        </is>
+      </c>
       <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one motivos_no_inspeccion</t>
+          <t>select_one tipos_inspeccion</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>motivo_no_inspeccion</t>
+          <t>tipo_inspeccion</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -599,16 +603,12 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} = 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>¿Por qué no se inspeccionó?</t>
+          <t>Tipo de inspección</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -617,12 +617,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one comunas</t>
+          <t>select_one motivos_no_inspeccion</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>comuna</t>
+          <t>motivo_no_inspeccion</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -630,17 +630,17 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} = 'no_inspeccionada'</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Comuna</t>
+          <t>¿Por qué no se inspeccionó?</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -649,29 +649,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one comunas</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>barrio</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
+          <t>comuna</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Barrio</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Nombre del barrio dentro de la comuna</t>
-        </is>
-      </c>
+          <t>Comuna</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
     </row>
     <row r="10">
@@ -682,7 +686,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>id_catastral</t>
+          <t>barrio</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -692,12 +696,12 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Identificación catastral</t>
+          <t>Barrio</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>sector-manzana-predio-mejora (IGAC), si se conoce</t>
+          <t>Nombre del barrio dentro de la comuna</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
@@ -710,26 +714,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>direccion</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>id_catastral</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Dirección de la edificación</t>
+          <t>Identificación catastral</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Como aparece en la placa, o la más aproximada</t>
+          <t>sector-manzana-predio-mejora (IGAC), si se conoce</t>
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
@@ -742,63 +742,63 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>nombre_edificacion</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>direccion</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Nombre de la edificación (si tiene)</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>Dirección de la edificación</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Como aparece en la placa, o la más aproximada</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>geopoint</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gps</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>nombre_edificacion</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Ubicación GPS</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Capturar de pie frente a la edificación, con cielo visible</t>
-        </is>
-      </c>
+          <t>Nombre de la edificación (si tiene)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>geopoint</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>pisos_sobre</t>
+          <t>gps</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -807,28 +807,20 @@
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 50</t>
-        </is>
-      </c>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niveles sobre el terreno</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 50</t>
-        </is>
-      </c>
+          <t>Ubicación GPS</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Capturar de pie frente a la edificación, con cielo visible</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -838,10 +830,14 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>sotanos</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>pisos_sobre</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
@@ -850,57 +846,57 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 10</t>
+          <t>. &gt;= 1 and . &lt;= 50</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Sótanos</t>
+          <t>Niveles sobre el terreno</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Debe estar entre 0 y 10</t>
+          <t>Debe estar entre 1 y 50</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one usos</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>uso_predominante</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+          <t>sotanos</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 10</t>
+        </is>
+      </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Uso predominante de la edificación</t>
+          <t>Sótanos</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Debe estar entre 0 y 10</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -910,10 +906,14 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>uso_planta_baja</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
+          <t>uso_predominante</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D17" t="inlineStr">
         <is>
           <t>minimal</t>
@@ -928,7 +928,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Uso de la planta baja</t>
+          <t>Uso predominante de la edificación</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -937,38 +937,34 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one usos</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>frente_m</t>
+          <t>uso_planta_baja</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>. &gt; 0 and . &lt; 1000</t>
-        </is>
-      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Frente aproximado (m)</t>
+          <t>Uso de la planta baja</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Valor en metros, mayor que 0</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -978,7 +974,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>fondo_m</t>
+          <t>frente_m</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -996,7 +992,7 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Fondo aproximado (m)</t>
+          <t>Frente aproximado (m)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -1009,51 +1005,55 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>select_one sistemas_estructurales</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>sistema_estructural</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+          <t>fondo_m</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>. &gt; 0 and . &lt; 1000</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Sistema estructural</t>
+          <t>Fondo aproximado (m)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Valor en metros, mayor que 0</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one tipos_entrepiso</t>
+          <t>select_one sistemas_estructurales</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>tipo_entrepiso</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>sistema_estructural</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>minimal</t>
@@ -1068,7 +1068,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Tipo de entrepiso</t>
+          <t>Sistema estructural</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1077,20 +1077,20 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one rangos_ano</t>
+          <t>select_one tipos_entrepiso</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>rango_ano</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>tipo_entrepiso</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
@@ -1100,7 +1100,7 @@
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Año de construcción</t>
+          <t>Tipo de entrepiso</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1109,12 +1109,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one colapsos</t>
+          <t>select_one rangos_ano</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>colapso</t>
+          <t>rango_ano</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1132,7 +1132,7 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Colapso</t>
+          <t>Año de construcción</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -1141,12 +1141,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one inclinaciones</t>
+          <t>select_one colapsos</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>inclinacion</t>
+          <t>colapso</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1164,7 +1164,7 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Inclinación de la edificación o de un piso</t>
+          <t>Colapso</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -1173,12 +1173,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one inclinaciones</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>piso_mayor_dano</t>
+          <t>inclinacion</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1189,40 +1189,28 @@
       <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and ${colapso} != 'total'</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 50</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>¿Cuál es el piso de mayor daño?</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>La matriz de daño se evalúa en ese piso</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>0 = sótano; máximo 50</t>
-        </is>
-      </c>
+          <t>Inclinación de la edificación o de un piso</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>dano_vigas</t>
+          <t>piso_mayor_dano</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1233,28 +1221,40 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and ${colapso} != 'total'</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 50</t>
+        </is>
+      </c>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Daño en vigas</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+          <t>¿Cuál es el piso de mayor daño?</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>La matriz de daño se evalúa en ese piso</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0 = sótano; máximo 50</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dano_vigas_pct</t>
+          <t>dano_vigas</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1265,36 +1265,28 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_vigas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr">
         <is>
-          <t>% de extensión del daño en vigas</t>
+          <t>Daño en vigas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dano_columnas</t>
+          <t>dano_vigas_pct</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1305,28 +1297,36 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_vigas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Daño en columnas</t>
+          <t>% de extensión del daño en vigas</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dano_columnas_pct</t>
+          <t>dano_columnas</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1337,36 +1337,28 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_columnas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>% de extensión del daño en columnas</t>
+          <t>Daño en columnas</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dano_nudos</t>
+          <t>dano_columnas_pct</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1377,28 +1369,36 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14')</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_columnas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Daño en nudos (unión viga-columna)</t>
+          <t>% de extensión del daño en columnas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>dano_nudos_pct</t>
+          <t>dano_nudos</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1409,36 +1409,28 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14') and ${dano_nudos} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14')</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>% de extensión del daño en nudos (unión viga-columna)</t>
+          <t>Daño en nudos (unión viga-columna)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>dano_conexiones</t>
+          <t>dano_nudos_pct</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1449,28 +1441,36 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14') and ${dano_nudos} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Daño en conexiones</t>
+          <t>% de extensión del daño en nudos (unión viga-columna)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>dano_conexiones_pct</t>
+          <t>dano_conexiones</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1481,36 +1481,28 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_conexiones} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr">
         <is>
-          <t>% de extensión del daño en conexiones</t>
+          <t>Daño en conexiones</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>dano_muros</t>
+          <t>dano_conexiones_pct</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1521,28 +1513,36 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13')</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_conexiones} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Daño en muros estructurales</t>
+          <t>% de extensión del daño en conexiones</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dano_muros_pct</t>
+          <t>dano_muros</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1553,36 +1553,28 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13') and ${dano_muros} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13')</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>% de extensión del daño en muros estructurales</t>
+          <t>Daño en muros estructurales</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>dano_muros_portantes</t>
+          <t>dano_muros_pct</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1593,28 +1585,36 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13') and ${dano_muros} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Daño en muros portantes</t>
+          <t>% de extensión del daño en muros estructurales</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>dano_muros_portantes_pct</t>
+          <t>dano_muros_portantes</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1625,36 +1625,28 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_muros_portantes} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
-          <t>% de extensión del daño en muros portantes</t>
+          <t>Daño en muros portantes</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dano_columnetas</t>
+          <t>dano_muros_portantes_pct</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1665,28 +1657,36 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_muros_portantes} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Daño en columnetas de confinamiento</t>
+          <t>% de extensión del daño en muros portantes</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>dano_columnetas_pct</t>
+          <t>dano_columnetas</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1697,36 +1697,28 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_columnetas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
-          <t>% de extensión del daño en columnetas de confinamiento</t>
+          <t>Daño en columnetas de confinamiento</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dano_vigas_confinamiento</t>
+          <t>dano_columnetas_pct</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1737,28 +1729,36 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_columnetas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Daño en vigas de confinamiento</t>
+          <t>% de extensión del daño en columnetas de confinamiento</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>dano_vigas_confinamiento_pct</t>
+          <t>dano_vigas_confinamiento</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1769,36 +1769,28 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_vigas_confinamiento} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
-          <t>% de extensión del daño en vigas de confinamiento</t>
+          <t>Daño en vigas de confinamiento</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>dano_entrepisos</t>
+          <t>dano_vigas_confinamiento_pct</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1809,28 +1801,36 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_vigas_confinamiento} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Daño en entrepisos</t>
+          <t>% de extensión del daño en vigas de confinamiento</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>dano_entrepisos_pct</t>
+          <t>dano_entrepisos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1841,36 +1841,28 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_entrepisos} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
-          <t>% de extensión del daño en entrepisos</t>
+          <t>Daño en entrepisos</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>select_multiple senales</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>senales_alarma</t>
+          <t>dano_entrepisos_pct</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1881,40 +1873,36 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_entrepisos} != 'ninguno'</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
+          <t>. &gt;= 1 and . &lt;= 100</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Señales de alarma observadas</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Marcar todas las que apliquen; si no hay, marcar «Ninguna»</t>
-        </is>
-      </c>
+          <t>% de extensión del daño en entrepisos</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
-          <t>«Ninguna» no puede combinarse con otras señales</t>
+          <t>Debe estar entre 1 y 100</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>select_one danos_globales</t>
+          <t>select_multiple senales</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dano_global</t>
+          <t>senales_alarma</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1928,25 +1916,37 @@
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Porcentaje global de daño de la edificación</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
+          <t>Señales de alarma observadas</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Marcar todas las que apliquen; si no hay, marcar «Ninguna»</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>«Ninguna» no puede combinarse con otras señales</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>select_one danos_globales</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>foto_fachada</t>
+          <t>dano_global</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1955,23 +1955,19 @@
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
       <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Foto: fachada completa</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Desde el frente, que se vea todo el edificio</t>
-        </is>
-      </c>
+          <t>Porcentaje global de daño de la edificación</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -1982,7 +1978,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>foto_esquina_1</t>
+          <t>foto_fachada</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2000,10 +1996,14 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Foto: esquina 1</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>Foto: fachada completa</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Desde el frente, que se vea todo el edificio</t>
+        </is>
+      </c>
       <c r="J47" t="inlineStr"/>
     </row>
     <row r="48">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>foto_esquina_2</t>
+          <t>foto_esquina_1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2032,7 +2032,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Foto: esquina 2</t>
+          <t>Foto: esquina 1</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -2046,10 +2046,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>foto_esquina_3</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+          <t>foto_esquina_2</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr"/>
       <c r="F49" t="inlineStr"/>
@@ -2060,7 +2064,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Foto: esquina 3 (si es accesible)</t>
+          <t>Foto: esquina 2</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -2074,7 +2078,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>foto_esquina_4</t>
+          <t>foto_esquina_3</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -2088,7 +2092,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Foto: esquina 4 (si es accesible)</t>
+          <t>Foto: esquina 3 (si es accesible)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -2102,36 +2106,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>foto_grieta</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>foto_esquina_4</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>max-pixels=2048</t>
+          <t>max-pixels=1600</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Foto: peor grieta, de cerca</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Poner una moneda junto a la grieta como referencia de escala</t>
-        </is>
-      </c>
+          <t>Foto: esquina 4 (si es accesible)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
     </row>
     <row r="52">
@@ -2142,7 +2134,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>foto_columnas</t>
+          <t>foto_grieta</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2159,16 +2151,56 @@
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
+          <t>max-pixels=2048</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Foto: peor grieta, de cerca</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Poner una moneda junto a la grieta como referencia de escala</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>foto_columnas</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
           <t>max-pixels=1600</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>Foto: columnas del primer piso</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr"/>
+      <c r="I53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2181,7 +2213,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C96"/>
+  <dimension ref="A1:C98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2204,34 +2236,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>tipos_inspeccion</t>
+          <t>confirmaciones</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>exterior</t>
+          <t>si</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Solo exterior</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>tipos_inspeccion</t>
+          <t>confirmaciones</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>parcial</t>
+          <t>no_aplica</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Parcial (exterior + algunas zonas interiores)</t>
+          <t>No aplica (inmueble desocupado o sin acceso)</t>
         </is>
       </c>
     </row>
@@ -2243,12 +2275,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>completa</t>
+          <t>exterior</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Completa</t>
+          <t>Solo exterior</t>
         </is>
       </c>
     </row>
@@ -2260,46 +2292,46 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no_inspeccionada</t>
+          <t>parcial</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No se inspeccionó</t>
+          <t>Parcial (exterior + algunas zonas interiores)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>motivos_no_inspeccion</t>
+          <t>tipos_inspeccion</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>no_permitido</t>
+          <t>completa</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>No se permitió el acceso</t>
+          <t>Completa</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>motivos_no_inspeccion</t>
+          <t>tipos_inspeccion</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>desocupada</t>
+          <t>no_inspeccionada</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Edificación desocupada</t>
+          <t>No se inspeccionó</t>
         </is>
       </c>
     </row>
@@ -2311,12 +2343,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>colapso</t>
+          <t>no_permitido</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Colapso total</t>
+          <t>No se permitió el acceso</t>
         </is>
       </c>
     </row>
@@ -2328,12 +2360,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>demolida</t>
+          <t>desocupada</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ya demolida</t>
+          <t>Edificación desocupada</t>
         </is>
       </c>
     </row>
@@ -2345,46 +2377,46 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>colapso</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Colapso total</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>motivos_no_inspeccion</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>centro</t>
+          <t>demolida</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Centro</t>
+          <t>Ya demolida</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>motivos_no_inspeccion</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>rio_otun</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Río Otún</t>
+          <t>Otro</t>
         </is>
       </c>
     </row>
@@ -2396,12 +2428,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>villavicencio</t>
+          <t>centro</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Villavicencio</t>
+          <t>Centro</t>
         </is>
       </c>
     </row>
@@ -2413,12 +2445,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>villa_santana</t>
+          <t>rio_otun</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Villa Santana</t>
+          <t>Río Otún</t>
         </is>
       </c>
     </row>
@@ -2430,12 +2462,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>oriente</t>
+          <t>villavicencio</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Oriente</t>
+          <t>Villavicencio</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2479,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>villa_santana</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Universidad</t>
+          <t>Villa Santana</t>
         </is>
       </c>
     </row>
@@ -2464,12 +2496,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>boston</t>
+          <t>oriente</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston</t>
+          <t>Oriente</t>
         </is>
       </c>
     </row>
@@ -2481,12 +2513,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Jardín</t>
+          <t>Universidad</t>
         </is>
       </c>
     </row>
@@ -2498,12 +2530,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>cuba</t>
+          <t>boston</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Boston</t>
         </is>
       </c>
     </row>
@@ -2515,12 +2547,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>consota</t>
+          <t>jardin</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Consotá</t>
+          <t>Jardín</t>
         </is>
       </c>
     </row>
@@ -2532,12 +2564,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>el_oso</t>
+          <t>cuba</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>El Oso</t>
+          <t>Cuba</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2581,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>san_joaquin</t>
+          <t>consota</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Consotá</t>
         </is>
       </c>
     </row>
@@ -2566,12 +2598,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>perla_del_otun</t>
+          <t>el_oso</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Perla del Otún</t>
+          <t>El Oso</t>
         </is>
       </c>
     </row>
@@ -2583,12 +2615,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>olimpica</t>
+          <t>san_joaquin</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Olímpica</t>
+          <t>San Joaquín</t>
         </is>
       </c>
     </row>
@@ -2600,12 +2632,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ferrocarril</t>
+          <t>perla_del_otun</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Ferrocarril</t>
+          <t>Perla del Otún</t>
         </is>
       </c>
     </row>
@@ -2617,12 +2649,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>del_cafe</t>
+          <t>olimpica</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Del Café</t>
+          <t>Olímpica</t>
         </is>
       </c>
     </row>
@@ -2634,12 +2666,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>el_poblado</t>
+          <t>ferrocarril</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>El Poblado</t>
+          <t>Ferrocarril</t>
         </is>
       </c>
     </row>
@@ -2651,12 +2683,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>el_rocio</t>
+          <t>del_cafe</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>El Rocío</t>
+          <t>Del Café</t>
         </is>
       </c>
     </row>
@@ -2668,12 +2700,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>san_nicolas</t>
+          <t>el_poblado</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>El Poblado</t>
         </is>
       </c>
     </row>
@@ -2685,46 +2717,46 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>el_rocio</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Otra / zona rural</t>
+          <t>El Rocío</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>san_nicolas</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Concreto: pórtico</t>
+          <t>San Nicolás</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Concreto: muros estructurales</t>
+          <t>Otra / zona rural</t>
         </is>
       </c>
     </row>
@@ -2736,12 +2768,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Concreto: sistema dual (pórtico + muros)</t>
+          <t>Concreto: pórtico</t>
         </is>
       </c>
     </row>
@@ -2753,12 +2785,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Concreto: prefabricado</t>
+          <t>Concreto: muros estructurales</t>
         </is>
       </c>
     </row>
@@ -2770,12 +2802,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mampostería confinada (con vigas y columnas de amarre)</t>
+          <t>Concreto: sistema dual (pórtico + muros)</t>
         </is>
       </c>
     </row>
@@ -2787,12 +2819,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mampostería reforzada</t>
+          <t>Concreto: prefabricado</t>
         </is>
       </c>
     </row>
@@ -2804,12 +2836,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mampostería no reforzada (sin amarres)</t>
+          <t>Mampostería confinada (con vigas y columnas de amarre)</t>
         </is>
       </c>
     </row>
@@ -2821,12 +2853,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Acero: pórticos arriostrados</t>
+          <t>Mampostería reforzada</t>
         </is>
       </c>
     </row>
@@ -2838,12 +2870,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Acero: pórticos no arriostrados</t>
+          <t>Mampostería no reforzada (sin amarres)</t>
         </is>
       </c>
     </row>
@@ -2855,12 +2887,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Acero: pórticos en celosía</t>
+          <t>Acero: pórticos arriostrados</t>
         </is>
       </c>
     </row>
@@ -2872,12 +2904,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Madera: pórticos y panel en madera</t>
+          <t>Acero: pórticos no arriostrados</t>
         </is>
       </c>
     </row>
@@ -2889,12 +2921,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Madera: pórticos con paneles de otros materiales</t>
+          <t>Acero: pórticos en celosía</t>
         </is>
       </c>
     </row>
@@ -2906,12 +2938,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Muros en bahareque</t>
+          <t>Madera: pórticos y panel en madera</t>
         </is>
       </c>
     </row>
@@ -2923,12 +2955,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Muros en tapia</t>
+          <t>Madera: pórticos con paneles de otros materiales</t>
         </is>
       </c>
     </row>
@@ -2940,12 +2972,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Muros en bahareque</t>
         </is>
       </c>
     </row>
@@ -2957,46 +2989,46 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Otros / no identificable</t>
+          <t>Muros en tapia</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Concreto: placa maciza</t>
+          <t>Mixta</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Concreto: placa aligerada</t>
+          <t>Otros / no identificable</t>
         </is>
       </c>
     </row>
@@ -3008,12 +3040,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Concreto: reticular celulado</t>
+          <t>Concreto: placa maciza</t>
         </is>
       </c>
     </row>
@@ -3025,12 +3057,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Acero: vigas alma llena con conectores</t>
+          <t>Concreto: placa aligerada</t>
         </is>
       </c>
     </row>
@@ -3042,12 +3074,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Acero: vigas alma llena sin conectores</t>
+          <t>Concreto: reticular celulado</t>
         </is>
       </c>
     </row>
@@ -3059,12 +3091,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Acero: cerchas</t>
+          <t>Acero: vigas alma llena con conectores</t>
         </is>
       </c>
     </row>
@@ -3076,12 +3108,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Madera: vigas</t>
+          <t>Acero: vigas alma llena sin conectores</t>
         </is>
       </c>
     </row>
@@ -3093,12 +3125,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Madera: cerchas</t>
+          <t>Acero: cerchas</t>
         </is>
       </c>
     </row>
@@ -3110,12 +3142,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Madera: vigas</t>
         </is>
       </c>
     </row>
@@ -3127,46 +3159,46 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Otros / no se sabe</t>
+          <t>Madera: cerchas</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Mixta</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Comercial</t>
+          <t>Otros / no se sabe</t>
         </is>
       </c>
     </row>
@@ -3178,12 +3210,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Educacional</t>
+          <t>Residencial</t>
         </is>
       </c>
     </row>
@@ -3195,12 +3227,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Comercial</t>
         </is>
       </c>
     </row>
@@ -3212,12 +3244,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hotelero</t>
+          <t>Educacional</t>
         </is>
       </c>
     </row>
@@ -3229,12 +3261,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Oficinas</t>
+          <t>Salud</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3278,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Hotelero</t>
         </is>
       </c>
     </row>
@@ -3263,12 +3295,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Institucional</t>
+          <t>Oficinas</t>
         </is>
       </c>
     </row>
@@ -3280,12 +3312,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bodegas</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
@@ -3297,12 +3329,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Estacionamientos</t>
+          <t>Institucional</t>
         </is>
       </c>
     </row>
@@ -3314,46 +3346,46 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Bodegas</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>rangos_ano</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Antes de 1950</t>
+          <t>Estacionamientos</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>rangos_ano</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>1950 – 1982</t>
+          <t>Otros</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3397,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>1982 – 1997</t>
+          <t>Antes de 1950</t>
         </is>
       </c>
     </row>
@@ -3382,46 +3414,46 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1998 en adelante</t>
+          <t>1950 – 1982</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>colapsos</t>
+          <t>rangos_ano</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Colapso total</t>
+          <t>1982 – 1997</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>colapsos</t>
+          <t>rangos_ano</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>parcial_mayor_50</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Colapso parcial (50% o más)</t>
+          <t>1998 en adelante</t>
         </is>
       </c>
     </row>
@@ -3433,12 +3465,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>parcial_menor_50</t>
+          <t>total</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Colapso parcial (menos del 50%)</t>
+          <t>Colapso total</t>
         </is>
       </c>
     </row>
@@ -3450,46 +3482,46 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ninguno</t>
+          <t>parcial_mayor_50</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Colapso parcial (50% o más)</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>inclinaciones</t>
+          <t>colapsos</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>evidente</t>
+          <t>parcial_menor_50</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Inclinación evidente</t>
+          <t>Colapso parcial (menos del 50%)</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>inclinaciones</t>
+          <t>colapsos</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>dudas</t>
+          <t>ninguno</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hay dudas</t>
+          <t>Ninguno</t>
         </is>
       </c>
     </row>
@@ -3501,46 +3533,46 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>ninguna</t>
+          <t>evidente</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ninguna</t>
+          <t>Inclinación evidente</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>inclinaciones</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>ninguno</t>
+          <t>dudas</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Ninguno / muy leve</t>
+          <t>Hay dudas</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>inclinaciones</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>leve</t>
+          <t>ninguna</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Leve</t>
+          <t>Ninguna</t>
         </is>
       </c>
     </row>
@@ -3552,12 +3584,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>ninguno</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Ninguno / muy leve</t>
         </is>
       </c>
     </row>
@@ -3569,12 +3601,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>fuerte</t>
+          <t>leve</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fuerte</t>
+          <t>Leve</t>
         </is>
       </c>
     </row>
@@ -3586,46 +3618,46 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>severo</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Severo</t>
+          <t>Moderado</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>niveles_dano</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>ninguno</t>
+          <t>fuerte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Fuerte</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>niveles_dano</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>0_10</t>
+          <t>severo</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>0 – 10 %</t>
+          <t>Severo</t>
         </is>
       </c>
     </row>
@@ -3637,12 +3669,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>10_30</t>
+          <t>ninguno</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>10 – 30 %</t>
+          <t>Ninguno</t>
         </is>
       </c>
     </row>
@@ -3654,12 +3686,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>30_60</t>
+          <t>0_10</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>30 – 60 %</t>
+          <t>0 – 10 %</t>
         </is>
       </c>
     </row>
@@ -3671,12 +3703,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>60_100</t>
+          <t>10_30</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>60 – 100 %</t>
+          <t>10 – 30 %</t>
         </is>
       </c>
     </row>
@@ -3688,46 +3720,46 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>30_60</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>100 % (colapso)</t>
+          <t>30 – 60 %</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>danos_globales</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>grietas_x</t>
+          <t>60_100</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Grietas en X en muros</t>
+          <t>60 – 100 %</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>danos_globales</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>grietas_horizontales_base</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Grietas horizontales en base de columnas</t>
+          <t>100 % (colapso)</t>
         </is>
       </c>
     </row>
@@ -3739,12 +3771,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>refuerzo_expuesto</t>
+          <t>grietas_x</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Refuerzo (varillas) expuesto</t>
+          <t>Grietas en X en muros</t>
         </is>
       </c>
     </row>
@@ -3756,12 +3788,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>pisos_desnivelados</t>
+          <t>grietas_horizontales_base</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Pisos desnivelados o inclinados</t>
+          <t>Grietas horizontales en base de columnas</t>
         </is>
       </c>
     </row>
@@ -3773,12 +3805,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>separacion_muro_estructura</t>
+          <t>refuerzo_expuesto</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Separación entre muros y estructura</t>
+          <t>Refuerzo (varillas) expuesto</t>
         </is>
       </c>
     </row>
@@ -3790,12 +3822,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>grieta_ancha</t>
+          <t>pisos_desnivelados</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Grieta llamativamente ancha (fotografiar con escala)</t>
+          <t>Pisos desnivelados o inclinados</t>
         </is>
       </c>
     </row>
@@ -3807,10 +3839,44 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
+          <t>separacion_muro_estructura</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Separación entre muros y estructura</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>grieta_ancha</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Grieta llamativamente ancha (fotografiar con escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
           <t>ninguna</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C98" t="inlineStr">
         <is>
           <t>Ninguna</t>
         </is>
@@ -3865,7 +3931,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026081603</t>
+          <t>2026081604</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/kobo/ais.xlsx
+++ b/kobo/ais.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J53"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,15 +456,20 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>choice_filter</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>label::Español (es)</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>hint::Español (es)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>constraint_message::Español (es)</t>
         </is>
@@ -489,6 +494,7 @@
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -509,6 +515,7 @@
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -529,6 +536,7 @@
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -546,13 +554,14 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>AVISO DE PRIVACIDAD — Esta inspección registra ubicación, características y fotografías de la edificación (solo exteriores y elementos estructurales, no personas ni interiores habitados salvo lo estrictamente necesario) para priorizar la evaluación estructural post-sismo. Tratamiento según la Ley 1581 de 2012; política completa disponible con la entidad coordinadora. La clasificación resultante es un insumo de priorización: la habilitación definitiva es competencia de las autoridades.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -574,17 +583,18 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
         <is>
           <t>¿Informaste al ocupante o responsable del inmueble el propósito de la inspección y el aviso de privacidad?</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Si no hay nadie presente, marca «No aplica (inmueble desocupado o sin acceso)»</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -606,13 +616,14 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>Tipo de inspección</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -638,23 +649,24 @@
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
         <is>
           <t>¿Por qué no se inspeccionó?</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one comunas</t>
+          <t>select_one municipios</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>comuna</t>
+          <t>municipio</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -670,41 +682,51 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Comuna</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Municipio</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one comunas</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>barrio</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
+          <t>comuna</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Barrio</t>
+          <t>municipio = ${municipio}</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Nombre del barrio dentro de la comuna</t>
+          <t>Comuna</t>
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -714,7 +736,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>id_catastral</t>
+          <t>barrio</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
@@ -722,17 +744,18 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Identificación catastral</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr">
         <is>
-          <t>sector-manzana-predio-mejora (IGAC), si se conoce</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
+          <t>Barrio</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Nombre del barrio dentro de la comuna</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -742,29 +765,26 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>direccion</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>id_catastral</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Dirección de la edificación</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Como aparece en la placa, o la más aproximada</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>Identificación catastral</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>sector-manzana-predio-mejora (IGAC), si se conoce</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -774,63 +794,65 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>nombre_edificacion</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>direccion</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Nombre de la edificación (si tiene)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Dirección de la edificación</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Como aparece en la placa, o la más aproximada</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>geopoint</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gps</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>nombre_edificacion</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Ubicación GPS</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Capturar de pie frente a la edificación, con cielo visible</t>
+          <t>Nombre de la edificación (si tiene)</t>
         </is>
       </c>
       <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>geopoint</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>pisos_sobre</t>
+          <t>gps</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -839,28 +861,21 @@
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 50</t>
-        </is>
-      </c>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Niveles sobre el terreno</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Ubicación GPS</t>
+        </is>
+      </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Debe estar entre 1 y 50</t>
-        </is>
-      </c>
+          <t>Capturar de pie frente a la edificación, con cielo visible</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -870,10 +885,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>sotanos</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>pisos_sobre</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
@@ -882,57 +901,59 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 10</t>
+          <t>. &gt;= 1 and . &lt;= 50</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Sótanos</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Debe estar entre 0 y 10</t>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Niveles sobre el terreno</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 50</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one usos</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>uso_predominante</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+          <t>sotanos</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 10</t>
+        </is>
+      </c>
       <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Uso predominante de la edificación</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Sótanos</t>
+        </is>
+      </c>
       <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Debe estar entre 0 y 10</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -942,10 +963,14 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>uso_planta_baja</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
+          <t>uso_predominante</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>minimal</t>
@@ -958,49 +983,47 @@
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Uso de la planta baja</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Uso predominante de la edificación</t>
+        </is>
+      </c>
       <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one usos</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>frente_m</t>
+          <t>uso_planta_baja</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E19" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>. &gt; 0 and . &lt; 1000</t>
-        </is>
-      </c>
+      <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Frente aproximado (m)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Valor en metros, mayor que 0</t>
-        </is>
-      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Uso de la planta baja</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1010,7 +1033,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>fondo_m</t>
+          <t>frente_m</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
@@ -1026,13 +1049,14 @@
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Fondo aproximado (m)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Frente aproximado (m)</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
         <is>
           <t>Valor en metros, mayor que 0</t>
         </is>
@@ -1041,51 +1065,56 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>select_one sistemas_estructurales</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>sistema_estructural</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+          <t>fondo_m</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>. &gt; 0 and . &lt; 1000</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Sistema estructural</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Fondo aproximado (m)</t>
+        </is>
+      </c>
       <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Valor en metros, mayor que 0</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one tipos_entrepiso</t>
+          <t>select_one sistemas_estructurales</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>tipo_entrepiso</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>sistema_estructural</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
           <t>minimal</t>
@@ -1098,31 +1127,32 @@
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Tipo de entrepiso</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Sistema estructural</t>
+        </is>
+      </c>
       <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one rangos_ano</t>
+          <t>select_one tipos_entrepiso</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>rango_ano</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>tipo_entrepiso</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
@@ -1130,23 +1160,24 @@
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Año de construcción</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Tipo de entrepiso</t>
+        </is>
+      </c>
       <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one colapsos</t>
+          <t>select_one rangos_ano</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>colapso</t>
+          <t>rango_ano</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1162,23 +1193,24 @@
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Colapso</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Año de construcción</t>
+        </is>
+      </c>
       <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one inclinaciones</t>
+          <t>select_one colapsos</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>inclinacion</t>
+          <t>colapso</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1194,23 +1226,24 @@
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Inclinación de la edificación o de un piso</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Colapso</t>
+        </is>
+      </c>
       <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one inclinaciones</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>piso_mayor_dano</t>
+          <t>inclinacion</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1221,40 +1254,29 @@
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and ${colapso} != 'total'</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 50</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>¿Cuál es el piso de mayor daño?</t>
-        </is>
-      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
-          <t>La matriz de daño se evalúa en ese piso</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>0 = sótano; máximo 50</t>
-        </is>
-      </c>
+          <t>Inclinación de la edificación o de un piso</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>dano_vigas</t>
+          <t>piso_mayor_dano</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1265,28 +1287,41 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and ${colapso} != 'total'</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 50</t>
+        </is>
+      </c>
       <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Daño en vigas</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>¿Cuál es el piso de mayor daño?</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>La matriz de daño se evalúa en ese piso</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>0 = sótano; máximo 50</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dano_vigas_pct</t>
+          <t>dano_vigas</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1297,36 +1332,29 @@
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_vigas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en vigas</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Daño en vigas</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dano_columnas</t>
+          <t>dano_vigas_pct</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1337,28 +1365,37 @@
       <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_vigas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Daño en columnas</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en vigas</t>
+        </is>
+      </c>
       <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dano_columnas_pct</t>
+          <t>dano_columnas</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1369,36 +1406,29 @@
       <c r="D30" t="inlineStr"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_columnas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en columnas</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Daño en columnas</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>dano_nudos</t>
+          <t>dano_columnas_pct</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1409,28 +1439,37 @@
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14')</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_columnas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Daño en nudos (unión viga-columna)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en columnas</t>
+        </is>
+      </c>
       <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>dano_nudos_pct</t>
+          <t>dano_nudos</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1441,36 +1480,29 @@
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14') and ${dano_nudos} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14')</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en nudos (unión viga-columna)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Daño en nudos (unión viga-columna)</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>dano_conexiones</t>
+          <t>dano_nudos_pct</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1481,28 +1513,37 @@
       <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14') and ${dano_nudos} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Daño en conexiones</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en nudos (unión viga-columna)</t>
+        </is>
+      </c>
       <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>dano_conexiones_pct</t>
+          <t>dano_conexiones</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1513,36 +1554,29 @@
       <c r="D34" t="inlineStr"/>
       <c r="E34" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_conexiones} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en conexiones</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Daño en conexiones</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dano_muros</t>
+          <t>dano_conexiones_pct</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1553,28 +1587,37 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13')</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_conexiones} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Daño en muros estructurales</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en conexiones</t>
+        </is>
+      </c>
       <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>dano_muros_pct</t>
+          <t>dano_muros</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1585,36 +1628,29 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13') and ${dano_muros} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13')</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en muros estructurales</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Daño en muros estructurales</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>dano_muros_portantes</t>
+          <t>dano_muros_pct</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1625,28 +1661,37 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13') and ${dano_muros} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Daño en muros portantes</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en muros estructurales</t>
+        </is>
+      </c>
       <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dano_muros_portantes_pct</t>
+          <t>dano_muros_portantes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1657,36 +1702,29 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_muros_portantes} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en muros portantes</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Daño en muros portantes</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>dano_columnetas</t>
+          <t>dano_muros_portantes_pct</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1697,28 +1735,37 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_muros_portantes} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Daño en columnetas de confinamiento</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en muros portantes</t>
+        </is>
+      </c>
       <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dano_columnetas_pct</t>
+          <t>dano_columnetas</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1729,36 +1776,29 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_columnetas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en columnetas de confinamiento</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Daño en columnetas de confinamiento</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>dano_vigas_confinamiento</t>
+          <t>dano_columnetas_pct</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1769,28 +1809,37 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_columnetas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Daño en vigas de confinamiento</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en columnetas de confinamiento</t>
+        </is>
+      </c>
       <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>dano_vigas_confinamiento_pct</t>
+          <t>dano_vigas_confinamiento</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1801,36 +1850,29 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_vigas_confinamiento} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en vigas de confinamiento</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Daño en vigas de confinamiento</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>dano_entrepisos</t>
+          <t>dano_vigas_confinamiento_pct</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1841,28 +1883,37 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_vigas_confinamiento} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Daño en entrepisos</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en vigas de confinamiento</t>
+        </is>
+      </c>
       <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>dano_entrepisos_pct</t>
+          <t>dano_entrepisos</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1873,36 +1924,29 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_entrepisos} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en entrepisos</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Daño en entrepisos</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>select_multiple senales</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>senales_alarma</t>
+          <t>dano_entrepisos_pct</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1913,40 +1957,37 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_entrepisos} != 'ninguno'</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
+          <t>. &gt;= 1 and . &lt;= 100</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>Señales de alarma observadas</t>
-        </is>
-      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Marcar todas las que apliquen; si no hay, marcar «Ninguna»</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>«Ninguna» no puede combinarse con otras señales</t>
+          <t>% de extensión del daño en entrepisos</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>select_one danos_globales</t>
+          <t>select_multiple senales</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>dano_global</t>
+          <t>senales_alarma</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1960,25 +2001,38 @@
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
       <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>Porcentaje global de daño de la edificación</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Señales de alarma observadas</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Marcar todas las que apliquen; si no hay, marcar «Ninguna»</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>«Ninguna» no puede combinarse con otras señales</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>select_one danos_globales</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>foto_fachada</t>
+          <t>dano_global</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1987,24 +2041,21 @@
         </is>
       </c>
       <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
       <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>Foto: fachada completa</t>
-        </is>
-      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Desde el frente, que se vea todo el edificio</t>
+          <t>Porcentaje global de daño de la edificación</t>
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2014,7 +2065,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>foto_esquina_1</t>
+          <t>foto_fachada</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2030,13 +2081,18 @@
           <t>max-pixels=1600</t>
         </is>
       </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>Foto: esquina 1</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Foto: fachada completa</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Desde el frente, que se vea todo el edificio</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2046,7 +2102,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>foto_esquina_2</t>
+          <t>foto_esquina_1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2062,13 +2118,14 @@
           <t>max-pixels=1600</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>Foto: esquina 2</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Foto: esquina 1</t>
+        </is>
+      </c>
       <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2078,10 +2135,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>foto_esquina_3</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
+          <t>foto_esquina_2</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
@@ -2090,13 +2151,14 @@
           <t>max-pixels=1600</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Foto: esquina 3 (si es accesible)</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Foto: esquina 2</t>
+        </is>
+      </c>
       <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2106,7 +2168,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>foto_esquina_4</t>
+          <t>foto_esquina_3</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -2118,13 +2180,14 @@
           <t>max-pixels=1600</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>Foto: esquina 4 (si es accesible)</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Foto: esquina 3 (si es accesible)</t>
+        </is>
+      </c>
       <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2134,37 +2197,26 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>foto_grieta</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>foto_esquina_4</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr"/>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr">
         <is>
-          <t>max-pixels=2048</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Foto: peor grieta, de cerca</t>
-        </is>
-      </c>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Poner una moneda junto a la grieta como referencia de escala</t>
+          <t>Foto: esquina 4 (si es accesible)</t>
         </is>
       </c>
       <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2174,7 +2226,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>foto_columnas</t>
+          <t>foto_grieta</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2191,16 +2243,58 @@
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr">
         <is>
+          <t>max-pixels=2048</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Foto: peor grieta, de cerca</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Poner una moneda junto a la grieta como referencia de escala</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>foto_columnas</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
           <t>max-pixels=1600</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr">
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
         <is>
           <t>Foto: columnas del primer piso</t>
         </is>
       </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2213,7 +2307,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:D133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2232,6 +2326,11 @@
           <t>label::Español (es)</t>
         </is>
       </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>municipio</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2249,6 +2348,7 @@
           <t>Sí</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2266,6 +2366,7 @@
           <t>No aplica (inmueble desocupado o sin acceso)</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2283,6 +2384,7 @@
           <t>Solo exterior</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2300,6 +2402,7 @@
           <t>Parcial (exterior + algunas zonas interiores)</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2317,6 +2420,7 @@
           <t>Completa</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2334,6 +2438,7 @@
           <t>No se inspeccionó</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2351,6 +2456,7 @@
           <t>No se permitió el acceso</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2368,6 +2474,7 @@
           <t>Edificación desocupada</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2385,6 +2492,7 @@
           <t>Colapso total</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2402,6 +2510,7 @@
           <t>Ya demolida</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2419,125 +2528,133 @@
           <t>Otro</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>municipios</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>centro</t>
+          <t>66001</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Centro</t>
-        </is>
-      </c>
+          <t>Pereira</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>municipios</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>rio_otun</t>
+          <t>66170</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Río Otún</t>
-        </is>
-      </c>
+          <t>Dosquebradas</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>municipios</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>villavicencio</t>
+          <t>66682</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Villavicencio</t>
-        </is>
-      </c>
+          <t>Santa Rosa de Cabal</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>municipios</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>villa_santana</t>
+          <t>66400</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Villa Santana</t>
-        </is>
-      </c>
+          <t>La Virginia</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>municipios</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>oriente</t>
+          <t>76001</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Oriente</t>
-        </is>
-      </c>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>municipios</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>27001</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Universidad</t>
-        </is>
-      </c>
+          <t>Quibdó</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>municipios</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>boston</t>
+          <t>otro</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston</t>
-        </is>
-      </c>
+          <t>Otro municipio</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2547,12 +2664,17 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>centro</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Jardín</t>
+          <t>Centro</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2564,12 +2686,17 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>cuba</t>
+          <t>rio_otun</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Río Otún</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2581,12 +2708,17 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>consota</t>
+          <t>villavicencio</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Consotá</t>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2598,12 +2730,17 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>el_oso</t>
+          <t>villa_santana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>El Oso</t>
+          <t>Villa Santana</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2615,12 +2752,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>san_joaquin</t>
+          <t>oriente</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
+          <t>Oriente</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2632,12 +2774,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>perla_del_otun</t>
+          <t>universidad</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Perla del Otún</t>
+          <t>Universidad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2649,12 +2796,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>olimpica</t>
+          <t>boston</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Olímpica</t>
+          <t>Boston</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2818,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>ferrocarril</t>
+          <t>jardin</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Ferrocarril</t>
+          <t>Jardín</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2683,12 +2840,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>del_cafe</t>
+          <t>cuba</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Del Café</t>
+          <t>Cuba</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2700,12 +2862,17 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>el_poblado</t>
+          <t>consota</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>El Poblado</t>
+          <t>Consotá</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2717,12 +2884,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>el_rocio</t>
+          <t>el_oso</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>El Rocío</t>
+          <t>El Oso</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2734,12 +2906,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>san_nicolas</t>
+          <t>san_joaquin</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
+          <t>San Joaquín</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
@@ -2751,1136 +2928,1977 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>perla_del_otun</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Otra / zona rural</t>
+          <t>Perla del Otún</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>olimpica</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Concreto: pórtico</t>
+          <t>Olímpica</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>ferrocarril</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Concreto: muros estructurales</t>
+          <t>Ferrocarril</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>del_cafe</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Concreto: sistema dual (pórtico + muros)</t>
+          <t>Del Café</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>el_poblado</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Concreto: prefabricado</t>
+          <t>El Poblado</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>el_rocio</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Mampostería confinada (con vigas y columnas de amarre)</t>
+          <t>El Rocío</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>san_nicolas</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Mampostería reforzada</t>
+          <t>San Nicolás</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>cali_1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Mampostería no reforzada (sin amarres)</t>
+          <t>Comuna 1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>cali_2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Acero: pórticos arriostrados</t>
+          <t>Comuna 2</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>cali_3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Acero: pórticos no arriostrados</t>
+          <t>Comuna 3</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>cali_4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Acero: pórticos en celosía</t>
+          <t>Comuna 4</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>cali_5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Madera: pórticos y panel en madera</t>
+          <t>Comuna 5</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>cali_6</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Madera: pórticos con paneles de otros materiales</t>
+          <t>Comuna 6</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>cali_7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Muros en bahareque</t>
+          <t>Comuna 7</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>cali_8</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Muros en tapia</t>
+          <t>Comuna 8</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>cali_9</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Comuna 9</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>cali_10</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Otros / no identificable</t>
+          <t>Comuna 10</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>cali_11</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Concreto: placa maciza</t>
+          <t>Comuna 11</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>cali_12</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Concreto: placa aligerada</t>
+          <t>Comuna 12</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>cali_13</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Concreto: reticular celulado</t>
+          <t>Comuna 13</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>cali_14</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Acero: vigas alma llena con conectores</t>
+          <t>Comuna 14</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>cali_15</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Acero: vigas alma llena sin conectores</t>
+          <t>Comuna 15</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>cali_16</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Acero: cerchas</t>
+          <t>Comuna 16</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>cali_17</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Madera: vigas</t>
+          <t>Comuna 17</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>cali_18</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Madera: cerchas</t>
+          <t>Comuna 18</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>cali_19</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Comuna 19</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>cali_20</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Otros / no se sabe</t>
+          <t>Comuna 20</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>cali_21</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Residencial</t>
+          <t>Comuna 21</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>cali_22</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Comercial</t>
+          <t>Comuna 22</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>otra_66001</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Educacional</t>
+          <t>Otra / zona rural</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>66001</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>otra_66170</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Salud</t>
+          <t>Otra / zona rural</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>66170</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>otra_66682</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hotelero</t>
+          <t>Otra / zona rural</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>66682</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>otra_66400</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Oficinas</t>
+          <t>Otra / zona rural</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>66400</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>otra_76001</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Industrial</t>
+          <t>Otra / zona rural</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>76001</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>otra_27001</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Institucional</t>
+          <t>Otra / zona rural</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>27001</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>comunas</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bodegas</t>
+          <t>Otra / zona rural</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>otro</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Estacionamientos</t>
-        </is>
-      </c>
+          <t>Concreto: pórtico</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>usos</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Otros</t>
-        </is>
-      </c>
+          <t>Concreto: muros estructurales</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>rangos_ano</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Antes de 1950</t>
-        </is>
-      </c>
+          <t>Concreto: sistema dual (pórtico + muros)</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>rangos_ano</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>1950 – 1982</t>
-        </is>
-      </c>
+          <t>Concreto: prefabricado</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>rangos_ano</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>1982 – 1997</t>
-        </is>
-      </c>
+          <t>Mampostería confinada (con vigas y columnas de amarre)</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>rangos_ano</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>1998 en adelante</t>
-        </is>
-      </c>
+          <t>Mampostería reforzada</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>colapsos</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Colapso total</t>
-        </is>
-      </c>
+          <t>Mampostería no reforzada (sin amarres)</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>colapsos</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>parcial_mayor_50</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Colapso parcial (50% o más)</t>
-        </is>
-      </c>
+          <t>Acero: pórticos arriostrados</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>colapsos</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>parcial_menor_50</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Colapso parcial (menos del 50%)</t>
-        </is>
-      </c>
+          <t>Acero: pórticos no arriostrados</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>colapsos</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ninguno</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+          <t>Acero: pórticos en celosía</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>inclinaciones</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>evidente</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Inclinación evidente</t>
-        </is>
-      </c>
+          <t>Madera: pórticos y panel en madera</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>inclinaciones</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>dudas</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hay dudas</t>
-        </is>
-      </c>
+          <t>Madera: pórticos con paneles de otros materiales</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>inclinaciones</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ninguna</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
+          <t>Muros en bahareque</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ninguno</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ninguno / muy leve</t>
-        </is>
-      </c>
+          <t>Muros en tapia</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>leve</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Leve</t>
-        </is>
-      </c>
+          <t>Mixta</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Moderado</t>
-        </is>
-      </c>
+          <t>Otros / no identificable</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>fuerte</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Fuerte</t>
-        </is>
-      </c>
+          <t>Concreto: placa maciza</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>severo</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Severo</t>
-        </is>
-      </c>
+          <t>Concreto: placa aligerada</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ninguno</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
+          <t>Concreto: reticular celulado</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>0_10</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>0 – 10 %</t>
-        </is>
-      </c>
+          <t>Acero: vigas alma llena con conectores</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>10_30</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>10 – 30 %</t>
-        </is>
-      </c>
+          <t>Acero: vigas alma llena sin conectores</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>30_60</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>30 – 60 %</t>
-        </is>
-      </c>
+          <t>Acero: cerchas</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>60_100</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>60 – 100 %</t>
-        </is>
-      </c>
+          <t>Madera: vigas</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>100 % (colapso)</t>
-        </is>
-      </c>
+          <t>Madera: cerchas</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>grietas_x</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Grietas en X en muros</t>
-        </is>
-      </c>
+          <t>Mixta</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>grietas_horizontales_base</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Grietas horizontales en base de columnas</t>
-        </is>
-      </c>
+          <t>Otros / no se sabe</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>refuerzo_expuesto</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Refuerzo (varillas) expuesto</t>
-        </is>
-      </c>
+          <t>Residencial</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>pisos_desnivelados</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Pisos desnivelados o inclinados</t>
-        </is>
-      </c>
+          <t>Comercial</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>separacion_muro_estructura</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Separación entre muros y estructura</t>
-        </is>
-      </c>
+          <t>Educacional</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>grieta_ancha</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Grieta llamativamente ancha (fotografiar con escala)</t>
-        </is>
-      </c>
+          <t>Salud</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
+          <t>usos</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Hotelero</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>usos</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Oficinas</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>usos</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Industrial</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>usos</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Institucional</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>usos</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Bodegas</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>usos</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Estacionamientos</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>usos</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>rangos_ano</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Antes de 1950</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>rangos_ano</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>1950 – 1982</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>rangos_ano</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>1982 – 1997</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>rangos_ano</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>1998 en adelante</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>colapsos</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>total</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Colapso total</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>colapsos</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>parcial_mayor_50</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Colapso parcial (50% o más)</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>colapsos</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>parcial_menor_50</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Colapso parcial (menos del 50%)</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>colapsos</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>inclinaciones</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>evidente</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Inclinación evidente</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>inclinaciones</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>dudas</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Hay dudas</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>inclinaciones</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>ninguna</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Ninguna</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>niveles_dano</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Ninguno / muy leve</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>niveles_dano</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>leve</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>niveles_dano</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>moderado</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>niveles_dano</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>fuerte</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Fuerte</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>niveles_dano</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>severo</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Severo</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>0_10</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>0 – 10 %</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>10_30</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>10 – 30 %</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>30_60</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>30 – 60 %</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>60_100</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>60 – 100 %</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>100 % (colapso)</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
           <t>senales</t>
         </is>
       </c>
-      <c r="B98" t="inlineStr">
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>grietas_x</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Grietas en X en muros</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>grietas_horizontales_base</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Grietas horizontales en base de columnas</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>refuerzo_expuesto</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Refuerzo (varillas) expuesto</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>pisos_desnivelados</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Pisos desnivelados o inclinados</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>separacion_muro_estructura</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Separación entre muros y estructura</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>grieta_ancha</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Grieta llamativamente ancha (fotografiar con escala)</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
         <is>
           <t>ninguna</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr">
+      <c r="C133" t="inlineStr">
         <is>
           <t>Ninguna</t>
         </is>
       </c>
+      <c r="D133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3931,7 +4949,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026081604</t>
+          <t>2026081605</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/kobo/ais.xlsx
+++ b/kobo/ais.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K54"/>
+  <dimension ref="A1:L65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,15 +461,20 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>default</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>label::Español (es)</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>hint::Español (es)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>constraint_message::Español (es)</t>
         </is>
@@ -495,6 +500,7 @@
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -516,6 +522,7 @@
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -537,6 +544,7 @@
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -555,13 +563,14 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>AVISO DE PRIVACIDAD — Esta inspección registra ubicación, características y fotografías de la edificación (solo exteriores y elementos estructurales, no personas ni interiores habitados salvo lo estrictamente necesario) para priorizar la evaluación estructural post-sismo. Tratamiento según la Ley 1581 de 2012; política completa disponible con la entidad coordinadora. La clasificación resultante es un insumo de priorización: la habilitación definitiva es competencia de las autoridades.</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -584,17 +593,18 @@
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>¿Informaste al ocupante o responsable del inmueble el propósito de la inspección y el aviso de privacidad?</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>Si no hay nadie presente, marca «No aplica (inmueble desocupado o sin acceso)»</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -617,13 +627,14 @@
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>Tipo de inspección</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -650,18 +661,19 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>¿Por qué no se inspeccionó?</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one municipios</t>
+          <t>select_one_from_file municipios.csv</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -683,23 +695,24 @@
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one comunas</t>
+          <t>select_one tipo_zona</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>comuna</t>
+          <t>tipo_zona</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -707,94 +720,113 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>municipio = ${municipio}</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Comuna</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Tipo de zona</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one_from_file divisiones.csv</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>barrio</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
+          <t>division_urbana</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>${tipo_zona} = 'urbano'</t>
+        </is>
+      </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Barrio</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>municipio_code=${municipio} and tipo='urbano'</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Nombre del barrio dentro de la comuna</t>
+          <t>Comuna</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one_from_file divisiones.csv</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>id_catastral</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
+          <t>division_rural</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>${tipo_zona} = 'rural'</t>
+        </is>
+      </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>Identificación catastral</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>municipio_code=${municipio} and tipo='rural'</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
-          <t>sector-manzana-predio-mejora (IGAC), si se conoce</t>
+          <t>Corregimiento</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one_from_file barrios.csv</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>direccion</t>
+          <t>barrio</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -802,22 +834,27 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>Dirección de la edificación</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>division_code=if(${tipo_zona} = 'urbano', ${division_urbana}, ${division_rural}) or name='OTRO'</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Como aparece en la placa, o la más aproximada</t>
+          <t>Barrio / Vereda</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -827,446 +864,371 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>nombre_edificacion</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>barrio_otro</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>${barrio} = 'OTRO'</t>
+        </is>
+      </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>Nombre de la edificación (si tiene)</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>¿Cuál?</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>geopoint</t>
+          <t>select_one via_tipo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>gps</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>via_tipo</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>${tipo_zona} = 'urbano'</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>Ubicación GPS</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Capturar de pie frente a la edificación, con cielo visible</t>
+          <t>Tipo de vía</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>pisos_sobre</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>via_numero</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 50</t>
-        </is>
-      </c>
+          <t>${tipo_zona} = 'urbano'</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>Niveles sobre el terreno</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 50</t>
-        </is>
-      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Número de vía</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>sotanos</t>
+          <t>numero_placa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 10</t>
-        </is>
-      </c>
+          <t>${tipo_zona} = 'urbano'</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>Sótanos</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>Debe estar entre 0 y 10</t>
-        </is>
-      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Número (placa)</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>select_one usos</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>uso_predominante</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+          <t>referencia_ubicacion</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>Uso predominante de la edificación</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Referencia de ubicación</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Finca, kilómetro, punto de referencia</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>select_one usos</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>uso_planta_baja</t>
+          <t>nombre_edificacion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Uso de la planta baja</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Nombre de la edificación (si tiene)</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Propiedad horizontal o institución</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>geopoint</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>frente_m</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>. &gt; 0 and . &lt; 1000</t>
-        </is>
-      </c>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>Frente aproximado (m)</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Ubicación GPS</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Valor en metros, mayor que 0</t>
-        </is>
-      </c>
+          <t>Capturar de pie frente a la edificación, con cielo visible. Si no captura bajo techo, reintentar afuera.</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>fondo_m</t>
+          <t>catastral</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>. &gt; 0 and . &lt; 1000</t>
-        </is>
-      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>Fondo aproximado (m)</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Identificación catastral (opcional)</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Valor en metros, mayor que 0</t>
-        </is>
-      </c>
+          <t>Solo si tiene el recibo de predial a la vista</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>select_one sistemas_estructurales</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>sistema_estructural</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+          <t>cat_sector</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>Sistema estructural</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>select_one tipos_entrepiso</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>tipo_entrepiso</t>
+          <t>cat_manzana</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Tipo de entrepiso</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Manzana</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>select_one rangos_ano</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>rango_ano</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>cat_predio</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>Año de construcción</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Predio</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>select_one colapsos</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>colapso</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>cat_mejora</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Colapso</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Mejora / Prop. horizontal</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>select_one inclinaciones</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>inclinacion</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="E26" t="inlineStr"/>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Inclinación de la edificación o de un piso</t>
-        </is>
-      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1276,7 +1238,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>piso_mayor_dano</t>
+          <t>pisos_sobre</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1287,74 +1249,76 @@
       <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and ${colapso} != 'total'</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 50</t>
+          <t>. &gt;= 1 and . &lt;= 50</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>¿Cuál es el piso de mayor daño?</t>
-        </is>
-      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
-          <t>La matriz de daño se evalúa en ese piso</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>0 = sótano; máximo 50</t>
+          <t>Niveles sobre el terreno</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 50</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>dano_vigas</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>sotanos</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 10</t>
+        </is>
+      </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Daño en vigas</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Sótanos</t>
+        </is>
+      </c>
       <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Debe estar entre 0 y 10</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one usos</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>dano_vigas_pct</t>
+          <t>uso_predominante</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1362,147 +1326,147 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_vigas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en vigas</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Uso predominante de la edificación</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>select_one usos</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>dano_columnas</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr"/>
+          <t>uso_planta_baja</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Daño en columnas</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Uso de la planta baja</t>
+        </is>
+      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>dano_columnas_pct</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>frente_m</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_columnas} != 'ninguno'</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
+          <t>. &gt; 0 and . &lt; 1000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en columnas</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Frente aproximado (m)</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Valor en metros, mayor que 0</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>dano_nudos</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>fondo_m</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14')</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>. &gt; 0 and . &lt; 1000</t>
+        </is>
+      </c>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Daño en nudos (unión viga-columna)</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Fondo aproximado (m)</t>
+        </is>
+      </c>
       <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>Valor en metros, mayor que 0</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one sistemas_estructurales</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>dano_nudos_pct</t>
+          <t>sistema_estructural</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1510,73 +1474,71 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14') and ${dano_nudos} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en nudos (unión viga-columna)</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Sistema estructural</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>select_one tipos_entrepiso</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>dano_conexiones</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
+          <t>tipo_entrepiso</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Daño en conexiones</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Tipo de entrepiso</t>
+        </is>
+      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one rangos_ano</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>dano_conexiones_pct</t>
+          <t>rango_ano</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1587,37 +1549,30 @@
       <c r="D35" t="inlineStr"/>
       <c r="E35" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_conexiones} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en conexiones</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Año de construcción</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>select_one colapsos</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>dano_muros</t>
+          <t>colapso</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1628,29 +1583,30 @@
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13')</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Daño en muros estructurales</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Colapso</t>
+        </is>
+      </c>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one inclinaciones</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>dano_muros_pct</t>
+          <t>inclinacion</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1661,37 +1617,30 @@
       <c r="D37" t="inlineStr"/>
       <c r="E37" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13') and ${dano_muros} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en muros estructurales</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Inclinación de la edificación o de un piso</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>dano_muros_portantes</t>
+          <t>piso_mayor_dano</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1702,29 +1651,42 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and ${colapso} != 'total'</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 50</t>
+        </is>
+      </c>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Daño en muros portantes</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>¿Cuál es el piso de mayor daño?</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>La matriz de daño se evalúa en ese piso</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0 = sótano; máximo 50</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>dano_muros_portantes_pct</t>
+          <t>dano_vigas</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1735,37 +1697,30 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_muros_portantes} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en muros portantes</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Daño en vigas</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dano_columnetas</t>
+          <t>dano_vigas_pct</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1776,29 +1731,38 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_vigas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Daño en columnetas de confinamiento</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en vigas</t>
+        </is>
+      </c>
       <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>dano_columnetas_pct</t>
+          <t>dano_columnas</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1809,37 +1773,30 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_columnetas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en columnetas de confinamiento</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Daño en columnas</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>dano_vigas_confinamiento</t>
+          <t>dano_columnas_pct</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1850,29 +1807,38 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_columnas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Daño en vigas de confinamiento</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en columnas</t>
+        </is>
+      </c>
       <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>dano_vigas_confinamiento_pct</t>
+          <t>dano_nudos</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1883,37 +1849,30 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_vigas_confinamiento} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14')</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en vigas de confinamiento</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Daño en nudos (unión viga-columna)</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>dano_entrepisos</t>
+          <t>dano_nudos_pct</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1924,29 +1883,38 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14') and ${dano_nudos} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Daño en entrepisos</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en nudos (unión viga-columna)</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dano_entrepisos_pct</t>
+          <t>dano_conexiones</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1957,37 +1925,30 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_entrepisos} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en entrepisos</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Daño en conexiones</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>select_multiple senales</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>senales_alarma</t>
+          <t>dano_conexiones_pct</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1998,41 +1959,38 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_conexiones} != 'ninguno'</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
+          <t>. &gt;= 1 and . &lt;= 100</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>Señales de alarma observadas</t>
-        </is>
-      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Marcar todas las que apliquen; si no hay, marcar «Ninguna»</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>«Ninguna» no puede combinarse con otras señales</t>
+          <t>% de extensión del daño en conexiones</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>select_one danos_globales</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>dano_global</t>
+          <t>dano_muros</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2043,29 +2001,30 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13')</t>
         </is>
       </c>
       <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>Porcentaje global de daño de la edificación</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Daño en muros estructurales</t>
+        </is>
+      </c>
       <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>foto_fachada</t>
+          <t>dano_muros_pct</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2074,35 +2033,40 @@
         </is>
       </c>
       <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13') and ${dano_muros} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>Foto: fachada completa</t>
-        </is>
-      </c>
+      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Desde el frente, que se vea todo el edificio</t>
+          <t>% de extensión del daño en muros estructurales</t>
         </is>
       </c>
       <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>foto_esquina_1</t>
+          <t>dano_muros_portantes</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2111,31 +2075,32 @@
         </is>
       </c>
       <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
+        </is>
+      </c>
       <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>Foto: esquina 1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Daño en muros portantes</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>foto_esquina_2</t>
+          <t>dano_muros_portantes_pct</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2144,89 +2109,116 @@
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_muros_portantes} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>Foto: esquina 2</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en muros portantes</t>
+        </is>
+      </c>
       <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>foto_esquina_3</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
+          <t>dano_columnetas</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
+        </is>
+      </c>
       <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>Foto: esquina 3 (si es accesible)</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr"/>
+      <c r="I51" t="inlineStr"/>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Daño en columnetas de confinamiento</t>
+        </is>
+      </c>
       <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>foto_esquina_4</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>dano_columnetas_pct</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D52" t="inlineStr"/>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_columnetas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>Foto: esquina 4 (si es accesible)</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en columnetas de confinamiento</t>
+        </is>
+      </c>
       <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>foto_grieta</t>
+          <t>dano_vigas_confinamiento</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2237,37 +2229,30 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>max-pixels=2048</t>
-        </is>
-      </c>
+      <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>Foto: peor grieta, de cerca</t>
-        </is>
-      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Poner una moneda junto a la grieta como referencia de escala</t>
+          <t>Daño en vigas de confinamiento</t>
         </is>
       </c>
       <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>foto_columnas</t>
+          <t>dano_vigas_confinamiento_pct</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2278,23 +2263,430 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_vigas_confinamiento} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en vigas de confinamiento</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>select_one niveles_dano</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>dano_entrepisos</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr"/>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr"/>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Daño en entrepisos</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>dano_entrepisos_pct</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_entrepisos} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en entrepisos</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>select_multiple senales</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>senales_alarma</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr">
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Señales de alarma observadas</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Marcar todas las que apliquen; si no hay, marcar «Ninguna»</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>«Ninguna» no puede combinarse con otras señales</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>select_one danos_globales</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>dano_global</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr"/>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Porcentaje global de daño de la edificación</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>foto_fachada</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
         <is>
           <t>max-pixels=1600</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr"/>
-      <c r="I54" t="inlineStr">
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Foto: fachada completa</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Desde el frente, que se vea todo el edificio</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>foto_esquina_1</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Foto: esquina 1</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>foto_esquina_2</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr"/>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Foto: esquina 2</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>foto_esquina_3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>Foto: esquina 3 (si es accesible)</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>foto_esquina_4</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Foto: esquina 4 (si es accesible)</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>foto_grieta</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>max-pixels=2048</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Foto: peor grieta, de cerca</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Poner una moneda junto a la grieta como referencia de escala</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>foto_columnas</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr"/>
+      <c r="I65" t="inlineStr"/>
+      <c r="J65" t="inlineStr">
         <is>
           <t>Foto: columnas del primer piso</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
+      <c r="K65" t="inlineStr"/>
+      <c r="L65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2307,7 +2699,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D133"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2326,11 +2718,6 @@
           <t>label::Español (es)</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>municipio</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -2348,7 +2735,6 @@
           <t>Sí</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2366,7 +2752,6 @@
           <t>No aplica (inmueble desocupado o sin acceso)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2384,7 +2769,6 @@
           <t>Solo exterior</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2402,7 +2786,6 @@
           <t>Parcial (exterior + algunas zonas interiores)</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2420,7 +2803,6 @@
           <t>Completa</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2438,7 +2820,6 @@
           <t>No se inspeccionó</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2456,7 +2837,6 @@
           <t>No se permitió el acceso</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2474,7 +2854,6 @@
           <t>Edificación desocupada</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2492,7 +2871,6 @@
           <t>Colapso total</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2510,7 +2888,6 @@
           <t>Ya demolida</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2528,2377 +2905,1264 @@
           <t>Otro</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>municipios</t>
+          <t>tipo_zona</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>66001</t>
+          <t>urbano</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pereira</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr"/>
+          <t>Urbana</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>municipios</t>
+          <t>tipo_zona</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>66170</t>
+          <t>rural</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dosquebradas</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr"/>
+          <t>Rural</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>municipios</t>
+          <t>via_tipo</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>66682</t>
+          <t>carrera</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Santa Rosa de Cabal</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr"/>
+          <t>Carrera</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>municipios</t>
+          <t>via_tipo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>66400</t>
+          <t>calle</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>La Virginia</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Calle</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>municipios</t>
+          <t>via_tipo</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>76001</t>
+          <t>transversal</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cali</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
+          <t>Transversal</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>municipios</t>
+          <t>via_tipo</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>27001</t>
+          <t>diagonal</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Quibdó</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
+          <t>Diagonal</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>municipios</t>
+          <t>via_tipo</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>otro</t>
+          <t>avenida</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Otro municipio</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Avenida</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>via_tipo</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>centro</t>
+          <t>otra</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Centro</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Otra</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>rio_otun</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Río Otún</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Concreto: pórtico</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>villavicencio</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Villavicencio</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Concreto: muros estructurales</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>villa_santana</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Villa Santana</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Concreto: sistema dual (pórtico + muros)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>oriente</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oriente</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Concreto: prefabricado</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>universidad</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Universidad</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Mampostería confinada (con vigas y columnas de amarre)</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>boston</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Mampostería reforzada</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>jardin</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Jardín</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Mampostería no reforzada (sin amarres)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>cuba</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cuba</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Acero: pórticos arriostrados</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>consota</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Consotá</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Acero: pórticos no arriostrados</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>el_oso</t>
+          <t>33</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>El Oso</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Acero: pórticos en celosía</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>san_joaquin</t>
+          <t>41</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Joaquín</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Madera: pórticos y panel en madera</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>perla_del_otun</t>
+          <t>42</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Perla del Otún</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Madera: pórticos con paneles de otros materiales</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>olimpica</t>
+          <t>51</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Olímpica</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Muros en bahareque</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ferrocarril</t>
+          <t>52</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ferrocarril</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Muros en tapia</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>del_cafe</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Del Café</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Mixta</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>sistemas_estructurales</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>el_poblado</t>
+          <t>60</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>El Poblado</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Otros / no identificable</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>el_rocio</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>El Rocío</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Concreto: placa maciza</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>san_nicolas</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>San Nicolás</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>Concreto: placa aligerada</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>cali_1</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Comuna 1</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Concreto: reticular celulado</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>cali_2</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Comuna 2</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Acero: vigas alma llena con conectores</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>cali_3</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Comuna 3</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Acero: vigas alma llena sin conectores</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>cali_4</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Comuna 4</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Acero: cerchas</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>cali_5</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Comuna 5</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Madera: vigas</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>cali_6</t>
+          <t>32</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Comuna 6</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Madera: cerchas</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>cali_7</t>
+          <t>40</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Comuna 7</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Mixta</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>tipos_entrepiso</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>cali_8</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Comuna 8</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Otros / no se sabe</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>cali_9</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Comuna 9</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Residencial</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>cali_10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Comuna 10</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Comercial</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>cali_11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Comuna 11</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Educacional</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>cali_12</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Comuna 12</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Salud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>cali_13</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Comuna 13</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Hotelero</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>cali_14</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Comuna 14</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Oficinas</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>cali_15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Comuna 15</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Industrial</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>cali_16</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Comuna 16</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Institucional</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>cali_17</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Comuna 17</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Bodegas</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>cali_18</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Comuna 18</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Estacionamientos</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>usos</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>cali_19</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Comuna 19</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Otros</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>rangos_ano</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>cali_20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Comuna 20</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Antes de 1950</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>rangos_ano</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>cali_21</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Comuna 21</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>1950 – 1982</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>rangos_ano</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>cali_22</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Comuna 22</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>1982 – 1997</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>rangos_ano</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>otra_66001</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Otra / zona rural</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>66001</t>
+          <t>1998 en adelante</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>colapsos</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>otra_66170</t>
+          <t>total</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Otra / zona rural</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>66170</t>
+          <t>Colapso total</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>colapsos</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>otra_66682</t>
+          <t>parcial_mayor_50</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Otra / zona rural</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>66682</t>
+          <t>Colapso parcial (50% o más)</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>colapsos</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>otra_66400</t>
+          <t>parcial_menor_50</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Otra / zona rural</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>66400</t>
+          <t>Colapso parcial (menos del 50%)</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>colapsos</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>otra_76001</t>
+          <t>ninguno</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Otra / zona rural</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>76001</t>
+          <t>Ninguno</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>inclinaciones</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>otra_27001</t>
+          <t>evidente</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Otra / zona rural</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>27001</t>
+          <t>Inclinación evidente</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>comunas</t>
+          <t>inclinaciones</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>otra</t>
+          <t>dudas</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Otra / zona rural</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>otro</t>
+          <t>Hay dudas</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>inclinaciones</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>ninguna</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Concreto: pórtico</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Ninguna</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>niveles_dano</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>ninguno</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Concreto: muros estructurales</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Ninguno / muy leve</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>niveles_dano</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>leve</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Concreto: sistema dual (pórtico + muros)</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Leve</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>niveles_dano</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>moderado</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Concreto: prefabricado</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Moderado</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>niveles_dano</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>fuerte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Mampostería confinada (con vigas y columnas de amarre)</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Fuerte</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>niveles_dano</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>severo</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mampostería reforzada</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr"/>
+          <t>Severo</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>danos_globales</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>ninguno</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mampostería no reforzada (sin amarres)</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr"/>
+          <t>Ninguno</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>danos_globales</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>0_10</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Acero: pórticos arriostrados</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr"/>
+          <t>0 – 10 %</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>danos_globales</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>10_30</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Acero: pórticos no arriostrados</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr"/>
+          <t>10 – 30 %</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>danos_globales</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>30_60</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Acero: pórticos en celosía</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr"/>
+          <t>30 – 60 %</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>danos_globales</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>60_100</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Madera: pórticos y panel en madera</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr"/>
+          <t>60 – 100 %</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>danos_globales</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>100</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Madera: pórticos con paneles de otros materiales</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr"/>
+          <t>100 % (colapso)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>senales</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>grietas_x</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Muros en bahareque</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr"/>
+          <t>Grietas en X en muros</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>senales</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>grietas_horizontales_base</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Muros en tapia</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr"/>
+          <t>Grietas horizontales en base de columnas</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>senales</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>refuerzo_expuesto</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Mixta</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr"/>
+          <t>Refuerzo (varillas) expuesto</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>sistemas_estructurales</t>
+          <t>senales</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>pisos_desnivelados</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Otros / no identificable</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr"/>
+          <t>Pisos desnivelados o inclinados</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>senales</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>separacion_muro_estructura</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Concreto: placa maciza</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr"/>
+          <t>Separación entre muros y estructura</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>senales</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>grieta_ancha</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Concreto: placa aligerada</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr"/>
+          <t>Grieta llamativamente ancha (fotografiar con escala)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>tipos_entrepiso</t>
+          <t>senales</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>ninguna</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Concreto: reticular celulado</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>tipos_entrepiso</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Acero: vigas alma llena con conectores</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>tipos_entrepiso</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Acero: vigas alma llena sin conectores</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>tipos_entrepiso</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Acero: cerchas</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>tipos_entrepiso</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Madera: vigas</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>tipos_entrepiso</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Madera: cerchas</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr"/>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>tipos_entrepiso</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Mixta</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>tipos_entrepiso</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Otros / no se sabe</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>usos</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Residencial</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>usos</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Comercial</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>usos</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Educacional</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr"/>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>usos</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Salud</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr"/>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>usos</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Hotelero</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr"/>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>usos</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Oficinas</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr"/>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>usos</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Industrial</t>
-        </is>
-      </c>
-      <c r="D100" t="inlineStr"/>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>usos</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Institucional</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr"/>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>usos</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Bodegas</t>
-        </is>
-      </c>
-      <c r="D102" t="inlineStr"/>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>usos</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Estacionamientos</t>
-        </is>
-      </c>
-      <c r="D103" t="inlineStr"/>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>usos</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Otros</t>
-        </is>
-      </c>
-      <c r="D104" t="inlineStr"/>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>rangos_ano</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Antes de 1950</t>
-        </is>
-      </c>
-      <c r="D105" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>rangos_ano</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>1950 – 1982</t>
-        </is>
-      </c>
-      <c r="D106" t="inlineStr"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>rangos_ano</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>1982 – 1997</t>
-        </is>
-      </c>
-      <c r="D107" t="inlineStr"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>rangos_ano</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>1998 en adelante</t>
-        </is>
-      </c>
-      <c r="D108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>colapsos</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>total</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Colapso total</t>
-        </is>
-      </c>
-      <c r="D109" t="inlineStr"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>colapsos</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>parcial_mayor_50</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Colapso parcial (50% o más)</t>
-        </is>
-      </c>
-      <c r="D110" t="inlineStr"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>colapsos</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>parcial_menor_50</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Colapso parcial (menos del 50%)</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>colapsos</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>ninguno</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr"/>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>inclinaciones</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>evidente</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Inclinación evidente</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr"/>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>inclinaciones</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>dudas</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Hay dudas</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr"/>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>inclinaciones</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>ninguna</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
           <t>Ninguna</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr"/>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>niveles_dano</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>ninguno</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Ninguno / muy leve</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>niveles_dano</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>leve</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>Leve</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>niveles_dano</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>moderado</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Moderado</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr"/>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>niveles_dano</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>fuerte</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Fuerte</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr"/>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>niveles_dano</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>severo</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Severo</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr"/>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>danos_globales</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>ninguno</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Ninguno</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>danos_globales</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>0_10</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>0 – 10 %</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>danos_globales</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>10_30</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>10 – 30 %</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr"/>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>danos_globales</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>30_60</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>30 – 60 %</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr"/>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>danos_globales</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>60_100</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>60 – 100 %</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr"/>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>danos_globales</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>100 % (colapso)</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>senales</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>grietas_x</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Grietas en X en muros</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>senales</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>grietas_horizontales_base</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Grietas horizontales en base de columnas</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr"/>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>senales</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>refuerzo_expuesto</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Refuerzo (varillas) expuesto</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr"/>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>senales</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>pisos_desnivelados</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Pisos desnivelados o inclinados</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr"/>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>senales</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>separacion_muro_estructura</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Separación entre muros y estructura</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr"/>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>senales</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>grieta_ancha</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Grieta llamativamente ancha (fotografiar con escala)</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr"/>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>senales</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>ninguna</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Ninguna</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -4949,7 +4213,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026081605</t>
+          <t>2026081701</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">

--- a/kobo/ais.xlsx
+++ b/kobo/ais.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L65"/>
+  <dimension ref="A1:M66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -466,15 +466,20 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
+          <t>calculation</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>label::Español (es)</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>hint::Español (es)</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>constraint_message::Español (es)</t>
         </is>
@@ -501,6 +506,7 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,6 +529,7 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -545,6 +552,7 @@
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -564,13 +572,14 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
         <is>
           <t>AVISO DE PRIVACIDAD — Esta inspección registra ubicación, características y fotografías de la edificación (solo exteriores y elementos estructurales, no personas ni interiores habitados salvo lo estrictamente necesario) para priorizar la evaluación estructural post-sismo. Tratamiento según la Ley 1581 de 2012; política completa disponible con la entidad coordinadora. La clasificación resultante es un insumo de priorización: la habilitación definitiva es competencia de las autoridades.</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -594,17 +603,18 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
         <is>
           <t>¿Informaste al ocupante o responsable del inmueble el propósito de la inspección y el aviso de privacidad?</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>Si no hay nadie presente, marca «No aplica (inmueble desocupado o sin acceso)»</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -628,13 +638,14 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
         <is>
           <t>Tipo de inspección</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -662,13 +673,14 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr">
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
         <is>
           <t>¿Por qué no se inspeccionó?</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -696,13 +708,14 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr">
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
         <is>
           <t>Municipio</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -726,13 +739,14 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
         <is>
           <t>Tipo de zona</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -768,13 +782,14 @@
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
         <is>
           <t>Comuna</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -810,61 +825,51 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
         <is>
           <t>Corregimiento</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one_from_file barrios.csv</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>barrio</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+          <t>division_sel</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>division_code=if(${tipo_zona} = 'urbano', ${division_urbana}, ${division_rural}) or name='OTRO'</t>
-        </is>
-      </c>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Barrio / Vereda</t>
+          <t>if(${tipo_zona} = 'urbano', ${division_urbana}, ${division_rural})</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one_from_file barrios.csv</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>barrio_otro</t>
+          <t>barrio</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -872,63 +877,73 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>${barrio} = 'OTRO'</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>division_code=${division_sel} or name='OTRO'</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>¿Cuál?</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Barrio / Vereda</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one via_tipo</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>via_tipo</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
+          <t>barrio_otro</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>${tipo_zona} = 'urbano'</t>
+          <t>${barrio} = 'OTRO'</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Tipo de vía</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>¿Cuál?</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one via_tipo</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>via_numero</t>
+          <t>via_tipo</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
@@ -942,13 +957,14 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Número de vía</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tipo de vía</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -958,7 +974,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>numero_placa</t>
+          <t>via_numero</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -972,13 +988,14 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Número (placa)</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Número de vía</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -988,27 +1005,28 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>referencia_ubicacion</t>
+          <t>numero_placa</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>${tipo_zona} = 'urbano'</t>
+        </is>
+      </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Referencia de ubicación</t>
-        </is>
-      </c>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Finca, kilómetro, punto de referencia</t>
+          <t>Número (placa)</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1018,7 +1036,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>nombre_edificacion</t>
+          <t>referencia_ubicacion</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
@@ -1028,111 +1046,119 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Nombre de la edificación (si tiene)</t>
-        </is>
-      </c>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Propiedad horizontal o institución</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr"/>
+          <t>Referencia de ubicación</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Finca, kilómetro, punto de referencia</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>geopoint</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ubicacion</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>nombre_edificacion</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Ubicación GPS</t>
-        </is>
-      </c>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Capturar de pie frente a la edificación, con cielo visible. Si no captura bajo techo, reintentar afuera.</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr"/>
+          <t>Nombre de la edificación (si tiene)</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>Propiedad horizontal o institución</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>geopoint</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>catastral</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+          <t>ubicacion</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Identificación catastral (opcional)</t>
-        </is>
-      </c>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Solo si tiene el recibo de predial a la vista</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr"/>
+          <t>Ubicación GPS</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>Capturar de pie frente a la edificación, con cielo visible. Si no captura bajo techo, reintentar afuera.</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>cat_sector</t>
+          <t>catastral</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Sector</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Identificación catastral (opcional)</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>Solo si tiene el recibo de predial a la vista</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1142,7 +1168,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cat_manzana</t>
+          <t>cat_sector</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
@@ -1152,13 +1178,14 @@
       <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr"/>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Manzana</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Sector</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1168,7 +1195,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cat_predio</t>
+          <t>cat_manzana</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -1178,13 +1205,14 @@
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Predio</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Manzana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1194,7 +1222,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cat_mejora</t>
+          <t>cat_predio</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -1204,21 +1232,26 @@
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Mejora / Prop. horizontal</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Predio</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>cat_mejora</t>
+        </is>
+      </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr"/>
@@ -1227,50 +1260,32 @@
       <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Mejora / Prop. horizontal</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>pisos_sobre</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 50</t>
-        </is>
-      </c>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Niveles sobre el terreno</t>
-        </is>
-      </c>
+      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 50</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1280,10 +1295,14 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>sotanos</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
+          <t>pisos_sobre</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
@@ -1292,61 +1311,63 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 10</t>
+          <t>. &gt;= 1 and . &lt;= 50</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Sótanos</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>Debe estar entre 0 y 10</t>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Niveles sobre el terreno</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 50</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>select_one usos</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>uso_predominante</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+          <t>sotanos</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
       <c r="E29" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 10</t>
+        </is>
+      </c>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Uso predominante de la edificación</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Sótanos</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Debe estar entre 0 y 10</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1356,10 +1377,14 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>uso_planta_baja</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>uso_predominante</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
           <t>minimal</t>
@@ -1374,51 +1399,49 @@
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Uso de la planta baja</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Uso predominante de la edificación</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>select_one usos</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>frente_m</t>
+          <t>uso_planta_baja</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>. &gt; 0 and . &lt; 1000</t>
-        </is>
-      </c>
+      <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Frente aproximado (m)</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>Valor en metros, mayor que 0</t>
-        </is>
-      </c>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Uso de la planta baja</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1428,7 +1451,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>fondo_m</t>
+          <t>frente_m</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -1446,13 +1469,14 @@
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Fondo aproximado (m)</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Frente aproximado (m)</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
         <is>
           <t>Valor en metros, mayor que 0</t>
         </is>
@@ -1461,53 +1485,58 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>select_one sistemas_estructurales</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>sistema_estructural</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+          <t>fondo_m</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
       <c r="E33" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>. &gt; 0 and . &lt; 1000</t>
+        </is>
+      </c>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Sistema estructural</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Fondo aproximado (m)</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Valor en metros, mayor que 0</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_one tipos_entrepiso</t>
+          <t>select_one sistemas_estructurales</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>tipo_entrepiso</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>sistema_estructural</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
           <t>minimal</t>
@@ -1522,31 +1551,32 @@
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Tipo de entrepiso</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Sistema estructural</t>
+        </is>
+      </c>
       <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>select_one rangos_ano</t>
+          <t>select_one tipos_entrepiso</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>rango_ano</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr"/>
+          <t>tipo_entrepiso</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
@@ -1556,23 +1586,24 @@
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Año de construcción</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Tipo de entrepiso</t>
+        </is>
+      </c>
       <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>select_one colapsos</t>
+          <t>select_one rangos_ano</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>colapso</t>
+          <t>rango_ano</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1590,23 +1621,24 @@
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Colapso</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Año de construcción</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>select_one inclinaciones</t>
+          <t>select_one colapsos</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>inclinacion</t>
+          <t>colapso</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1624,23 +1656,24 @@
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Inclinación de la edificación o de un piso</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Colapso</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one inclinaciones</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>piso_mayor_dano</t>
+          <t>inclinacion</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1651,42 +1684,31 @@
       <c r="D38" t="inlineStr"/>
       <c r="E38" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and ${colapso} != 'total'</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 50</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
       <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>¿Cuál es el piso de mayor daño?</t>
-        </is>
-      </c>
+      <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>La matriz de daño se evalúa en ese piso</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>0 = sótano; máximo 50</t>
-        </is>
-      </c>
+          <t>Inclinación de la edificación o de un piso</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>dano_vigas</t>
+          <t>piso_mayor_dano</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1697,30 +1719,43 @@
       <c r="D39" t="inlineStr"/>
       <c r="E39" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and ${colapso} != 'total'</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 50</t>
+        </is>
+      </c>
       <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Daño en vigas</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>¿Cuál es el piso de mayor daño?</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>La matriz de daño se evalúa en ese piso</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>0 = sótano; máximo 50</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dano_vigas_pct</t>
+          <t>dano_vigas</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1731,38 +1766,31 @@
       <c r="D40" t="inlineStr"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_vigas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en vigas</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Daño en vigas</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>dano_columnas</t>
+          <t>dano_vigas_pct</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1773,30 +1801,39 @@
       <c r="D41" t="inlineStr"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_vigas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Daño en columnas</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en vigas</t>
+        </is>
+      </c>
       <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>dano_columnas_pct</t>
+          <t>dano_columnas</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1807,38 +1844,31 @@
       <c r="D42" t="inlineStr"/>
       <c r="E42" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_columnas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
       <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en columnas</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Daño en columnas</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>dano_nudos</t>
+          <t>dano_columnas_pct</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1849,30 +1879,39 @@
       <c r="D43" t="inlineStr"/>
       <c r="E43" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14')</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_columnas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>Daño en nudos (unión viga-columna)</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en columnas</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>dano_nudos_pct</t>
+          <t>dano_nudos</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1883,38 +1922,31 @@
       <c r="D44" t="inlineStr"/>
       <c r="E44" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14') and ${dano_nudos} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14')</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en nudos (unión viga-columna)</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Daño en nudos (unión viga-columna)</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dano_conexiones</t>
+          <t>dano_nudos_pct</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1925,30 +1957,39 @@
       <c r="D45" t="inlineStr"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14') and ${dano_nudos} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>Daño en conexiones</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en nudos (unión viga-columna)</t>
+        </is>
+      </c>
       <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>dano_conexiones_pct</t>
+          <t>dano_conexiones</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1959,38 +2000,31 @@
       <c r="D46" t="inlineStr"/>
       <c r="E46" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_conexiones} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en conexiones</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Daño en conexiones</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>dano_muros</t>
+          <t>dano_conexiones_pct</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2001,30 +2035,39 @@
       <c r="D47" t="inlineStr"/>
       <c r="E47" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13')</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_conexiones} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>Daño en muros estructurales</t>
-        </is>
-      </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en conexiones</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>dano_muros_pct</t>
+          <t>dano_muros</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2035,38 +2078,31 @@
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13') and ${dano_muros} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13')</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
       <c r="I48" t="inlineStr"/>
-      <c r="J48" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en muros estructurales</t>
-        </is>
-      </c>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Daño en muros estructurales</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>dano_muros_portantes</t>
+          <t>dano_muros_pct</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2077,30 +2113,39 @@
       <c r="D49" t="inlineStr"/>
       <c r="E49" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13') and ${dano_muros} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>Daño en muros portantes</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en muros estructurales</t>
+        </is>
+      </c>
       <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dano_muros_portantes_pct</t>
+          <t>dano_muros_portantes</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2111,38 +2156,31 @@
       <c r="D50" t="inlineStr"/>
       <c r="E50" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_muros_portantes} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
       <c r="I50" t="inlineStr"/>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en muros portantes</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Daño en muros portantes</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>dano_columnetas</t>
+          <t>dano_muros_portantes_pct</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2153,30 +2191,39 @@
       <c r="D51" t="inlineStr"/>
       <c r="E51" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_muros_portantes} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>Daño en columnetas de confinamiento</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en muros portantes</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dano_columnetas_pct</t>
+          <t>dano_columnetas</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2187,38 +2234,31 @@
       <c r="D52" t="inlineStr"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_columnetas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr"/>
       <c r="I52" t="inlineStr"/>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en columnetas de confinamiento</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Daño en columnetas de confinamiento</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>dano_vigas_confinamiento</t>
+          <t>dano_columnetas_pct</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2229,30 +2269,39 @@
       <c r="D53" t="inlineStr"/>
       <c r="E53" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_columnetas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>Daño en vigas de confinamiento</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr"/>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en columnetas de confinamiento</t>
+        </is>
+      </c>
       <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>dano_vigas_confinamiento_pct</t>
+          <t>dano_vigas_confinamiento</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2263,38 +2312,31 @@
       <c r="D54" t="inlineStr"/>
       <c r="E54" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_vigas_confinamiento} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en vigas de confinamiento</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Daño en vigas de confinamiento</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>dano_entrepisos</t>
+          <t>dano_vigas_confinamiento_pct</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2305,30 +2347,39 @@
       <c r="D55" t="inlineStr"/>
       <c r="E55" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr"/>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_vigas_confinamiento} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>Daño en entrepisos</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
+      <c r="J55" t="inlineStr"/>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en vigas de confinamiento</t>
+        </is>
+      </c>
       <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one niveles_dano</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>dano_entrepisos_pct</t>
+          <t>dano_entrepisos</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2339,38 +2390,31 @@
       <c r="D56" t="inlineStr"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_entrepisos} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en entrepisos</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Daño en entrepisos</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>select_multiple senales</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>senales_alarma</t>
+          <t>dano_entrepisos_pct</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2381,42 +2425,39 @@
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_entrepisos} != 'ninguno'</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
+          <t>. &gt;= 1 and . &lt;= 100</t>
         </is>
       </c>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>Señales de alarma observadas</t>
-        </is>
-      </c>
+      <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Marcar todas las que apliquen; si no hay, marcar «Ninguna»</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>«Ninguna» no puede combinarse con otras señales</t>
+          <t>% de extensión del daño en entrepisos</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>select_one danos_globales</t>
+          <t>select_multiple senales</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>dano_global</t>
+          <t>senales_alarma</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2430,27 +2471,40 @@
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
-      <c r="F58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>Porcentaje global de daño de la edificación</t>
-        </is>
-      </c>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
+      <c r="J58" t="inlineStr"/>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Señales de alarma observadas</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Marcar todas las que apliquen; si no hay, marcar «Ninguna»</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>«Ninguna» no puede combinarse con otras señales</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>select_one danos_globales</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>foto_fachada</t>
+          <t>dano_global</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2459,26 +2513,23 @@
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
-      <c r="E59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
       <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>Foto: fachada completa</t>
-        </is>
-      </c>
+      <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Desde el frente, que se vea todo el edificio</t>
+          <t>Porcentaje global de daño de la edificación</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2488,7 +2539,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>foto_esquina_1</t>
+          <t>foto_fachada</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2506,13 +2557,18 @@
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr">
-        <is>
-          <t>Foto: esquina 1</t>
-        </is>
-      </c>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Foto: fachada completa</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Desde el frente, que se vea todo el edificio</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2522,7 +2578,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>foto_esquina_2</t>
+          <t>foto_esquina_1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2540,13 +2596,14 @@
       </c>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>Foto: esquina 2</t>
-        </is>
-      </c>
-      <c r="K61" t="inlineStr"/>
+      <c r="J61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Foto: esquina 1</t>
+        </is>
+      </c>
       <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2556,10 +2613,14 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>foto_esquina_3</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
+          <t>foto_esquina_2</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" t="inlineStr"/>
       <c r="F62" t="inlineStr"/>
@@ -2570,13 +2631,14 @@
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>Foto: esquina 3 (si es accesible)</t>
-        </is>
-      </c>
-      <c r="K62" t="inlineStr"/>
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Foto: esquina 2</t>
+        </is>
+      </c>
       <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2586,7 +2648,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>foto_esquina_4</t>
+          <t>foto_esquina_3</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -2600,13 +2662,14 @@
       </c>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>Foto: esquina 4 (si es accesible)</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Foto: esquina 3 (si es accesible)</t>
+        </is>
+      </c>
       <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2616,39 +2679,28 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>foto_grieta</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>foto_esquina_4</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="E64" t="inlineStr"/>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr">
         <is>
-          <t>max-pixels=2048</t>
+          <t>max-pixels=1600</t>
         </is>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>Foto: peor grieta, de cerca</t>
-        </is>
-      </c>
+      <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Poner una moneda junto a la grieta como referencia de escala</t>
+          <t>Foto: esquina 4 (si es accesible)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2658,7 +2710,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>foto_columnas</t>
+          <t>foto_grieta</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2675,18 +2727,62 @@
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr">
         <is>
-          <t>max-pixels=1600</t>
+          <t>max-pixels=2048</t>
         </is>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
-      <c r="J65" t="inlineStr">
+      <c r="J65" t="inlineStr"/>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Foto: peor grieta, de cerca</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Poner una moneda junto a la grieta como referencia de escala</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>foto_columnas</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
+      <c r="K66" t="inlineStr">
         <is>
           <t>Foto: columnas del primer piso</t>
         </is>
       </c>
-      <c r="K65" t="inlineStr"/>
-      <c r="L65" t="inlineStr"/>
+      <c r="L66" t="inlineStr"/>
+      <c r="M66" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/kobo/ais.xlsx
+++ b/kobo/ais.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M66"/>
+  <dimension ref="A1:M102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -557,16 +557,20 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>aviso_privacidad</t>
+          <t>intro</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
@@ -575,7 +579,7 @@
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
-          <t>AVISO DE PRIVACIDAD — Esta inspección registra ubicación, características y fotografías de la edificación (solo exteriores y elementos estructurales, no personas ni interiores habitados salvo lo estrictamente necesario) para priorizar la evaluación estructural post-sismo. Tratamiento según la Ley 1581 de 2012; política completa disponible con la entidad coordinadora. La clasificación resultante es un insumo de priorización: la habilitación definitiva es competencia de las autoridades.</t>
+          <t>Antes de empezar</t>
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
@@ -584,19 +588,15 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_one confirmaciones</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>aviso_comunicado</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>nota_rol</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr"/>
@@ -606,32 +606,24 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
-          <t>¿Informaste al ocupante o responsable del inmueble el propósito de la inspección y el aviso de privacidad?</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Si no hay nadie presente, marca «No aplica (inmueble desocupado o sin acceso)»</t>
-        </is>
-      </c>
+          <t>USTED DOCUMENTA, NO EVALÚA. Registre lo que observa y fotografíe: un ingeniero matriculado revisará este reporte y asignará la clasificación. Si tiene dudas en una pregunta, elija la opción más cercana a lo que ve y anótelo en «Comentarios» al final.</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>select_one tipos_inspeccion</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>tipo_inspeccion</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>nota_seguridad</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
@@ -641,7 +633,7 @@
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Tipo de inspección</t>
+          <t>⚠️ SU SEGURIDAD PRIMERO. No entre a edificaciones con daño evidente ni permanezca bajo balcones, fachadas o elementos que puedan caer. Todo lo importante se puede documentar desde el exterior.</t>
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
@@ -650,25 +642,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one motivos_no_inspeccion</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>motivo_no_inspeccion</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>aviso_privacidad</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} = 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -676,7 +660,7 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
-          <t>¿Por qué no se inspeccionó?</t>
+          <t>AVISO DE PRIVACIDAD — Esta inspección registra ubicación, características y fotografías de la edificación (solo exteriores y elementos estructurales, no personas ni interiores habitados salvo lo estrictamente necesario) para priorizar la evaluación estructural post-sismo. Tratamiento según la Ley 1581 de 2012; política completa disponible con la entidad coordinadora. La clasificación resultante es un insumo de priorización: la habilitación definitiva es competencia de las autoridades.</t>
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
@@ -685,12 +669,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>select_one_from_file municipios.csv</t>
+          <t>select_one confirmaciones</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>municipio</t>
+          <t>aviso_comunicado</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -698,11 +682,7 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr"/>
@@ -711,28 +691,28 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Municipio</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr"/>
+          <t>¿Informaste al ocupante o responsable del inmueble el propósito de la inspección y el aviso de privacidad?</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Si no hay nadie presente, marca «No aplica (inmueble desocupado o sin acceso)»</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>select_one tipo_zona</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>tipo_zona</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>codigo_comision</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr"/>
@@ -742,21 +722,25 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Tipo de zona</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr"/>
+          <t>Código de tu comisión o brigada</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>El asignado por la coordinación (ej.: BRG-05). Déjalo vacío si no te asignaron uno.</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one_from_file divisiones.csv</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>division_urbana</t>
+          <t>codigo_brigadista</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -764,112 +748,84 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>${tipo_zona} = 'urbano'</t>
-        </is>
-      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>municipio_code=${municipio} and tipo='urbano'</t>
-        </is>
-      </c>
+      <c r="H11" t="inlineStr"/>
       <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Comuna</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr"/>
+          <t>Tu código de brigadista o nombre completo</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Queda como responsable de la documentación de esta inspección</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>select_one_from_file divisiones.csv</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>division_rural</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>${tipo_zona} = 'rural'</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>municipio_code=${municipio} and tipo='rural'</t>
-        </is>
-      </c>
+      <c r="H12" t="inlineStr"/>
       <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>Corregimiento</t>
-        </is>
-      </c>
+      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>calculate</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>division_sel</t>
+          <t>inspeccion</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>if(${tipo_zona} = 'urbano', ${division_urbana}, ${division_rural})</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tipo de inspección</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_one_from_file barrios.csv</t>
+          <t>select_one tipos_inspeccion</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>barrio</t>
+          <t>tipo_inspeccion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -877,38 +833,34 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
+      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>division_code=${division_sel} or name='OTRO'</t>
-        </is>
-      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Barrio / Vereda</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr"/>
+          <t>¿Qué tipo de inspección pudiste hacer?</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>«Parcial» = exterior más algunas zonas interiores. Si no fue posible inspeccionar, igual registra ubicación y fotos: ese dato también sirve.</t>
+        </is>
+      </c>
       <c r="M14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one motivos_no_inspeccion</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>barrio_otro</t>
+          <t>motivo_no_inspeccion</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -919,7 +871,7 @@
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
-          <t>${barrio} = 'OTRO'</t>
+          <t>${tipo_inspeccion} = 'no_inspeccionada'</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
@@ -929,7 +881,7 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
-          <t>¿Cuál?</t>
+          <t>¿Por qué no se inspeccionó?</t>
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
@@ -938,52 +890,40 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>select_one via_tipo</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>via_tipo</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>${tipo_zona} = 'urbano'</t>
-        </is>
-      </c>
+      <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Tipo de vía</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>via_numero</t>
+          <t>ubicacion_grupo</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>${tipo_zona} = 'urbano'</t>
-        </is>
-      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -991,7 +931,7 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Número de vía</t>
+          <t>¿Dónde está la edificación?</t>
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
@@ -1000,21 +940,25 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one_from_file municipios.csv</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>numero_placa</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>${tipo_zona} = 'urbano'</t>
-        </is>
-      </c>
+          <t>municipio</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1022,7 +966,7 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Número (placa)</t>
+          <t>Municipio</t>
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
@@ -1031,15 +975,19 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one tipo_zona</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>referencia_ubicacion</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
+          <t>tipo_zona</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr"/>
@@ -1049,56 +997,64 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Referencia de ubicación</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Finca, kilómetro, punto de referencia</t>
-        </is>
-      </c>
+          <t>Tipo de zona</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one_from_file divisiones.csv</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>nombre_edificacion</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
+          <t>division_urbana</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>${tipo_zona} = 'urbano'</t>
+        </is>
+      </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>municipio_code=${municipio} and tipo='urbano'</t>
+        </is>
+      </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Nombre de la edificación (si tiene)</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>Propiedad horizontal o institución</t>
-        </is>
-      </c>
+          <t>Comuna</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>geopoint</t>
+          <t>select_one_from_file divisiones.csv</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ubicacion</t>
+          <t>division_rural</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1106,82 +1062,94 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>${tipo_zona} = 'rural'</t>
+        </is>
+      </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>municipio_code=${municipio} and tipo='rural'</t>
+        </is>
+      </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Ubicación GPS</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>Capturar de pie frente a la edificación, con cielo visible. Si no captura bajo techo, reintentar afuera.</t>
-        </is>
-      </c>
+          <t>Corregimiento</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>begin_group</t>
+          <t>calculate</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>catastral</t>
+          <t>division_sel</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>field-list</t>
-        </is>
-      </c>
+      <c r="D22" t="inlineStr"/>
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>Identificación catastral (opcional)</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Solo si tiene el recibo de predial a la vista</t>
-        </is>
-      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>if(${tipo_zona} = 'urbano', ${division_urbana}, ${division_rural})</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one_from_file barrios.csv</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>cat_sector</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+          <t>barrio</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>division_code=${division_sel} or name='OTRO'</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Sector</t>
+          <t>Barrio / Vereda</t>
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
@@ -1195,12 +1163,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>cat_manzana</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>barrio_otro</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
       <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>${barrio} = 'OTRO'</t>
+        </is>
+      </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr"/>
@@ -1208,7 +1184,7 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Manzana</t>
+          <t>¿Cuál?</t>
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
@@ -1217,17 +1193,21 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one via_tipo</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>cat_predio</t>
+          <t>via_tipo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>${tipo_zona} = 'urbano'</t>
+        </is>
+      </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr"/>
@@ -1235,7 +1215,7 @@
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Predio</t>
+          <t>Tipo de vía</t>
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
@@ -1249,12 +1229,16 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>cat_mejora</t>
+          <t>via_numero</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>${tipo_zona} = 'urbano'</t>
+        </is>
+      </c>
       <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr"/>
       <c r="H26" t="inlineStr"/>
@@ -1262,122 +1246,122 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Mejora / Prop. horizontal</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr"/>
+          <t>Número de vía</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>Ej.: para Carrera 7 # 45-12, aquí va el 7</t>
+        </is>
+      </c>
       <c r="M26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>end_group</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr"/>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>numero_placa</t>
+        </is>
+      </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>${tipo_zona} = 'urbano'</t>
+        </is>
+      </c>
       <c r="F27" t="inlineStr"/>
       <c r="G27" t="inlineStr"/>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Número (placa)</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>El resto de la dirección (45-12). Incluye interior, bloque o torre si es un conjunto.</t>
+        </is>
+      </c>
       <c r="M27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>pisos_sobre</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>referencia_ubicacion</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 50</t>
-        </is>
-      </c>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
       <c r="G28" t="inlineStr"/>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Niveles sobre el terreno</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 50</t>
-        </is>
-      </c>
+          <t>Referencia de ubicación</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Finca, kilómetro, punto de referencia. Si el sector tiene doble nomenclatura, anota la otra dirección en «Comentarios».</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>sotanos</t>
+          <t>nombre_edificacion</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>. &gt;= 0 and . &lt;= 10</t>
-        </is>
-      </c>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
       <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Sótanos</t>
-        </is>
-      </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Debe estar entre 0 y 10</t>
-        </is>
-      </c>
+          <t>Nombre de la edificación (si tiene)</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Propiedad horizontal o institución (ej.: Edificio Los Cámbulos, I.E. La Julita)</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>select_one usos</t>
+          <t>geopoint</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>uso_predominante</t>
+          <t>ubicacion</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1385,16 +1369,8 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr"/>
       <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr"/>
@@ -1402,34 +1378,30 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Uso predominante de la edificación</t>
-        </is>
-      </c>
-      <c r="L30" t="inlineStr"/>
+          <t>Ubicación GPS</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Capturar de pie frente a la edificación, con cielo visible. Si no captura bajo techo, reintentar afuera.</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>select_one usos</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>uso_planta_baja</t>
+          <t>catastral</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr"/>
       <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr"/>
@@ -1437,116 +1409,84 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Uso de la planta baja</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr"/>
+          <t>Identificación catastral (opcional)</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Solo si tiene el recibo de predial a la vista</t>
+        </is>
+      </c>
       <c r="M31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>frente_m</t>
+          <t>cat_sector</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>. &gt; 0 and . &lt; 1000</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr"/>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Frente aproximado (m)</t>
+          <t>Sector</t>
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Valor en metros, mayor que 0</t>
-        </is>
-      </c>
+      <c r="M32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>decimal</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>fondo_m</t>
+          <t>cat_manzana</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>. &gt; 0 and . &lt; 1000</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
       <c r="G33" t="inlineStr"/>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Fondo aproximado (m)</t>
+          <t>Manzana</t>
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Valor en metros, mayor que 0</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>select_one sistemas_estructurales</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>sistema_estructural</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+          <t>cat_predio</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr"/>
@@ -1554,7 +1494,7 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Sistema estructural</t>
+          <t>Predio</t>
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
@@ -1563,25 +1503,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>select_one tipos_entrepiso</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>tipo_entrepiso</t>
+          <t>cat_mejora</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>minimal</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr"/>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr"/>
@@ -1589,7 +1521,7 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Tipo de entrepiso</t>
+          <t>Mejora / Prop. horizontal</t>
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
@@ -1598,90 +1530,58 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>select_one rangos_ano</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>rango_ano</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr"/>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>Año de construcción</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>select_one colapsos</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>colapso</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr"/>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr"/>
       <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>Colapso</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>select_one inclinaciones</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>inclinacion</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>edificacion</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
@@ -1694,7 +1594,7 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Inclinación de la edificación o de un piso</t>
+          <t>La edificación</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -1708,7 +1608,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>piso_mayor_dano</t>
+          <t>pisos_sobre</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1717,14 +1617,10 @@
         </is>
       </c>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and ${colapso} != 'total'</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>. &gt;= 0 and . &lt;= 50</t>
+          <t>. &gt;= 1 and . &lt;= 50</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -1733,64 +1629,64 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr">
         <is>
-          <t>¿Cuál es el piso de mayor daño?</t>
+          <t>Niveles sobre el terreno</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>La matriz de daño se evalúa en ese piso</t>
+          <t>Sin contar cubierta ni terraza. Si está en ladera, cuenta desde la entrada principal.</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>0 = sótano; máximo 50</t>
+          <t>Debe estar entre 1 y 50</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>dano_vigas</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>sotanos</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 10</t>
+        </is>
+      </c>
       <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Daño en vigas</t>
+          <t>Sótanos</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Debe estar entre 0 y 10</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one usos</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>dano_vigas_pct</t>
+          <t>uso_predominante</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1798,55 +1694,47 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_vigas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
       <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr">
         <is>
-          <t>% de extensión del daño en vigas</t>
-        </is>
-      </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+          <t>Uso predominante de la edificación</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>Si hay varios usos, el que ocupa la mayor parte</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>select_one usos</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>dano_columnas</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
+          <t>uso_planta_baja</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr"/>
@@ -1854,37 +1742,33 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Daño en columnas</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr"/>
+          <t>Uso de la planta baja</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>Solo si es distinto del uso predominante (ej.: local comercial bajo apartamentos)</t>
+        </is>
+      </c>
       <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>dano_columnas_pct</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>frente_m</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_columnas} != 'ninguno'</t>
-        </is>
-      </c>
+      <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
+          <t>. &gt; 0 and . &lt; 1000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -1893,60 +1777,64 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr">
         <is>
-          <t>% de extensión del daño en columnas</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr"/>
+          <t>Frente aproximado (m)</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>Si no puede medir: un paso largo ≈ 1 m</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Debe estar entre 1 y 100</t>
+          <t>Valor en metros, mayor que 0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>decimal</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>dano_nudos</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>fondo_m</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14')</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>. &gt; 0 and . &lt; 1000</t>
+        </is>
+      </c>
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Daño en nudos (unión viga-columna)</t>
+          <t>Fondo aproximado (m)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Valor en metros, mayor que 0</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one habitada_opts</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>dano_nudos_pct</t>
+          <t>habitada</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1955,119 +1843,83 @@
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14') and ${dano_nudos} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr">
         <is>
-          <t>% de extensión del daño en nudos (unión viga-columna)</t>
+          <t>¿La edificación está habitada u ocupada actualmente?</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>dano_conexiones</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr"/>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
       <c r="F46" t="inlineStr"/>
       <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>Daño en conexiones</t>
-        </is>
-      </c>
+      <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>dano_conexiones_pct</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>estructura</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_conexiones} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr"/>
       <c r="K47" t="inlineStr">
         <is>
-          <t>% de extensión del daño en conexiones</t>
+          <t>¿De qué está hecha?</t>
         </is>
       </c>
       <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>select_one sistemas_estructurales</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>dano_muros</t>
+          <t>sistema_estructural</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2075,12 +1927,12 @@
           <t>yes</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13')</t>
-        </is>
-      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr"/>
       <c r="F48" t="inlineStr"/>
       <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr"/>
@@ -2088,64 +1940,60 @@
       <c r="J48" t="inlineStr"/>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Daño en muros estructurales</t>
-        </is>
-      </c>
-      <c r="L48" t="inlineStr"/>
+          <t>Sistema estructural</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Guía rápida: ¿esqueleto de columnas y vigas de concreto con muros solo de relleno? → Pórtico de concreto. ¿Muros de ladrillo que cargan la casa, con columnetas y vigas de amarre en concreto? → Mampostería confinada; sin amarres → no reforzada. ¿Esqueleto metálico? → acero. ¿Guadua o esterilla con revoque? → bahareque. ¿Muros gruesos de tierra pisada? → tapia. Si no logra identificarlo, elija «Otros / no identificable» y descríbalo en Comentarios.</t>
+        </is>
+      </c>
       <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one tipos_entrepiso</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>dano_muros_pct</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '12' or ${sistema_estructural} = '13') and ${dano_muros} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>tipo_entrepiso</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr"/>
       <c r="K49" t="inlineStr">
         <is>
-          <t>% de extensión del daño en muros estructurales</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+          <t>Tipo de entrepiso</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Lo que separa un piso de otro; suele verse desde abajo (el «techo» del primer piso). Si no lo distingue, «Otros / no se sabe».</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>select_one rangos_ano</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>dano_muros_portantes</t>
+          <t>rango_ano</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2154,11 +2002,7 @@
         </is>
       </c>
       <c r="D50" t="inlineStr"/>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
-        </is>
-      </c>
+      <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr"/>
@@ -2166,75 +2010,55 @@
       <c r="J50" t="inlineStr"/>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Daño en muros portantes</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr"/>
+          <t>Año de construcción</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Pregunte al ocupante o vecino. Si nadie lo sabe, marque «No se sabe»: no adivine.</t>
+        </is>
+      </c>
       <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>integer</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>dano_muros_portantes_pct</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr"/>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr"/>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_muros_portantes} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr"/>
       <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>% de extensión del daño en muros portantes</t>
-        </is>
-      </c>
+      <c r="K51" t="inlineStr"/>
       <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>dano_columnetas</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr"/>
+          <t>estado</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
@@ -2244,7 +2068,7 @@
       <c r="J52" t="inlineStr"/>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Daño en columnetas de confinamiento</t>
+          <t>Estado general y terreno</t>
         </is>
       </c>
       <c r="L52" t="inlineStr"/>
@@ -2253,12 +2077,12 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one colapsos</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>dano_columnetas_pct</t>
+          <t>colapso</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2267,41 +2091,33 @@
         </is>
       </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_columnetas} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
       <c r="K53" t="inlineStr">
         <is>
-          <t>% de extensión del daño en columnetas de confinamiento</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+          <t>Colapso</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>«Parcial» = una parte de la edificación cayó (un piso, un ala, la cubierta)</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>select_one inclinaciones</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>dano_vigas_confinamiento</t>
+          <t>inclinacion</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2310,11 +2126,7 @@
         </is>
       </c>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21')</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr"/>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr"/>
@@ -2322,21 +2134,25 @@
       <c r="J54" t="inlineStr"/>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Daño en vigas de confinamiento</t>
-        </is>
-      </c>
-      <c r="L54" t="inlineStr"/>
+          <t>Inclinación de la edificación o de un piso</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Compárela con las edificaciones vecinas o con un hilo con peso (plomada). Si no está seguro, «Hay dudas».</t>
+        </is>
+      </c>
       <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one asentamientos</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>dano_vigas_confinamiento_pct</t>
+          <t>asentamiento</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2345,41 +2161,33 @@
         </is>
       </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '21') and ${dano_vigas_confinamiento} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr">
         <is>
-          <t>% de extensión del daño en vigas de confinamiento</t>
-        </is>
-      </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+          <t>Asentamiento o hundimiento de la edificación</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>¿Se hundió o quedó más baja que el andén o los vecinos? ¿Aparecieron desniveles o escalones nuevos en el piso?</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>select_one niveles_dano</t>
+          <t>select_one fallas_talud</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>dano_entrepisos</t>
+          <t>falla_talud</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2388,11 +2196,7 @@
         </is>
       </c>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr"/>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr"/>
@@ -2400,122 +2204,86 @@
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Daño en entrepisos</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr"/>
+          <t>Falla en talud o movimiento en masa cerca</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Deslizamientos, caída de tierra o piedras, o grietas en el terreno alrededor de la edificación. «General» = afecta toda la ladera o varias edificaciones.</t>
+        </is>
+      </c>
       <c r="M56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>integer</t>
+          <t>select_one morfologias</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>dano_entrepisos_pct</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada' and (${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_entrepisos} != 'ninguno'</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>. &gt;= 1 and . &lt;= 100</t>
-        </is>
-      </c>
+          <t>morfologia</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>minimal</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
       <c r="K57" t="inlineStr">
         <is>
-          <t>% de extensión del daño en entrepisos</t>
+          <t>¿Cómo es el terreno donde está la edificación?</t>
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>Debe estar entre 1 y 100</t>
-        </is>
-      </c>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>select_multiple senales</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>senales_alarma</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr"/>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>Señales de alarma observadas</t>
-        </is>
-      </c>
-      <c r="L58" t="inlineStr">
-        <is>
-          <t>Marcar todas las que apliquen; si no hay, marcar «Ninguna»</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>«Ninguna» no puede combinarse con otras señales</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>select_one danos_globales</t>
+          <t>begin_group</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>dano_global</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>danos</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and ${colapso} != 'total'</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -2525,7 +2293,7 @@
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Porcentaje global de daño de la edificación</t>
+          <t>Daños en la estructura</t>
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
@@ -2534,12 +2302,12 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>integer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>foto_fachada</t>
+          <t>piso_mayor_dano</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2549,57 +2317,57 @@
       </c>
       <c r="D60" t="inlineStr"/>
       <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= ${pisos_sobre}</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Foto: fachada completa</t>
+          <t>¿Cuál es el piso de mayor daño?</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>Desde el frente, que se vea todo el edificio</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr"/>
+          <t>Las siguientes preguntas se responden mirando ese piso</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>0 = sótano; no puede ser mayor que el número de niveles</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>foto_esquina_1</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>guia_concreto</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14')</t>
+        </is>
+      </c>
       <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="G61" t="inlineStr"/>
       <c r="H61" t="inlineStr"/>
       <c r="I61" t="inlineStr"/>
       <c r="J61" t="inlineStr"/>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Foto: esquina 1</t>
+          <t>GUÍA para concreto — Ninguno: fisuras casi invisibles (&lt; 0,2 mm). Leve: se ven a simple vista (hasta 1 mm). Moderado: 1–2 mm o recubrimiento empezando a desprenderse. Fuerte: recubrimiento caído o varillas a la vista. Severo: concreto triturado, varillas dobladas, deformación evidente.</t>
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
@@ -2608,33 +2376,29 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>foto_esquina_2</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>guia_mamposteria</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23')</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="G62" t="inlineStr"/>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Foto: esquina 2</t>
+          <t>GUÍA para mampostería (ladrillo/bloque) — Ninguno: fisuras casi invisibles (&lt; 0,2 mm). Leve: hasta 1 mm. Moderado: 1–3 mm o inicio de grietas diagonales. Fuerte: grietas diagonales &gt; 3 mm o ladrillos dislocados. Severo: piezas desprendidas, aplastamiento o muro desplomado.</t>
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
@@ -2643,29 +2407,29 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>foto_esquina_3</t>
+          <t>guia_acero</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33')</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr"/>
       <c r="I63" t="inlineStr"/>
       <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr">
         <is>
-          <t>Foto: esquina 3 (si es accesible)</t>
+          <t>GUÍA para acero — Leve: deformaciones apenas perceptibles. Moderado: deformación visible o pandeo incipiente. Fuerte/Severo: pandeo o fractura clara, o soldaduras, tornillos o remaches rotos. Revise primero las conexiones y fotografíelas.</t>
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
@@ -2674,29 +2438,29 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>foto_esquina_4</t>
+          <t>guia_madera</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
-      <c r="E64" t="inlineStr"/>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
       <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
       <c r="K64" t="inlineStr">
         <is>
-          <t>Foto: esquina 4 (si es accesible)</t>
+          <t>GUÍA para madera — Leve: fisuras mínimas. Moderado: grietas con uniones aún firmes. Fuerte: uniones claramente corridas o desplazadas. Severo: pieza rota, seccionada o suelta de la estructura.</t>
         </is>
       </c>
       <c r="L64" t="inlineStr"/>
@@ -2705,84 +2469,1420 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>foto_grieta</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>guia_bahareque</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+          <t>(${sistema_estructural} = '51')</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>max-pixels=2048</t>
-        </is>
-      </c>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Foto: peor grieta, de cerca</t>
-        </is>
-      </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t>Poner una moneda junto a la grieta como referencia de escala</t>
-        </is>
-      </c>
+          <t>GUÍA para bahareque — Leve: grietas incipientes del revoque. Moderado: grietas en esquinas y revoque desprendiéndose. Fuerte: grietas en casi todos los muros o cubierta perdiendo apoyo. Severo: muro deformado o pandeado, pies derechos sueltos.</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>image</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>foto_columnas</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
+          <t>guia_tapia</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
       <c r="E66" t="inlineStr">
         <is>
-          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+          <t>(${sistema_estructural} = '52')</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>max-pixels=1600</t>
-        </is>
-      </c>
+      <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Foto: columnas del primer piso</t>
+          <t>GUÍA para tapia/adobe — Ninguno: fisuras &lt; 0,4 mm. Leve: 0,4–2 mm. Moderado: 2–4 mm. Fuerte: &gt; 4 mm o muro movido fuera de su plano. Severo: aplastamiento o desplome.</t>
         </is>
       </c>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>select_one niveles_dano</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>dano_vigas</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr"/>
+      <c r="I67" t="inlineStr"/>
+      <c r="J67" t="inlineStr"/>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Daño en vigas</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>dano_vigas_pct</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_vigas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr"/>
+      <c r="I68" t="inlineStr"/>
+      <c r="J68" t="inlineStr"/>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en vigas</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>De cada 10 vigas de ese piso, ¿cuántos tienen ese daño? 3 de cada 10 = 30</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>select_one niveles_dano</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>dano_columnas</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr"/>
+      <c r="I69" t="inlineStr"/>
+      <c r="J69" t="inlineStr"/>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Daño en columnas</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr"/>
+      <c r="M69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>dano_columnas_pct</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_columnas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
+      <c r="J70" t="inlineStr"/>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en columnas</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>De cada 10 columnas de ese piso, ¿cuántos tienen ese daño? 3 de cada 10 = 30</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>select_one niveles_dano</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>dano_nudos</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14')</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
+      <c r="J71" t="inlineStr"/>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Daño en nudos (unión viga-columna)</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr"/>
+      <c r="M71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>dano_nudos_pct</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14') and ${dano_nudos} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr"/>
+      <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en nudos (unión viga-columna)</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>De cada 10 nudos (unión viga-columna) de ese piso, ¿cuántos tienen ese daño? 3 de cada 10 = 30</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>select_one niveles_dano</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>dano_conexiones</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42')</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr"/>
+      <c r="I73" t="inlineStr"/>
+      <c r="J73" t="inlineStr"/>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Daño en conexiones</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr"/>
+      <c r="M73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>dano_conexiones_pct</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42') and ${dano_conexiones} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
+      <c r="I74" t="inlineStr"/>
+      <c r="J74" t="inlineStr"/>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en conexiones</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>De cada 10 conexiones de ese piso, ¿cuántos tienen ese daño? 3 de cada 10 = 30</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>select_one niveles_dano</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>dano_muros</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '12' or ${sistema_estructural} = '13')</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
+      <c r="I75" t="inlineStr"/>
+      <c r="J75" t="inlineStr"/>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Daño en muros estructurales</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr"/>
+      <c r="M75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>dano_muros_pct</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '12' or ${sistema_estructural} = '13') and ${dano_muros} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr"/>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
+      <c r="J76" t="inlineStr"/>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en muros estructurales</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>De cada 10 muros estructurales de ese piso, ¿cuántos tienen ese daño? 3 de cada 10 = 30</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>select_one niveles_dano</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>dano_muros_portantes</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr"/>
+      <c r="H77" t="inlineStr"/>
+      <c r="I77" t="inlineStr"/>
+      <c r="J77" t="inlineStr"/>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Daño en muros portantes</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr"/>
+      <c r="M77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>dano_muros_portantes_pct</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_muros_portantes} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr"/>
+      <c r="H78" t="inlineStr"/>
+      <c r="I78" t="inlineStr"/>
+      <c r="J78" t="inlineStr"/>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en muros portantes</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>De cada 10 muros portantes de ese piso, ¿cuántos tienen ese daño? 3 de cada 10 = 30</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>select_one niveles_dano</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>dano_columnetas</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '21')</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr"/>
+      <c r="H79" t="inlineStr"/>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Daño en columnetas de confinamiento</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr"/>
+      <c r="M79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>dano_columnetas_pct</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '21') and ${dano_columnetas} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en columnetas de confinamiento</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>De cada 10 columnetas de confinamiento de ese piso, ¿cuántos tienen ese daño? 3 de cada 10 = 30</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>select_one niveles_dano</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>dano_vigas_confinamiento</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '21')</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr"/>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Daño en vigas de confinamiento</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>dano_vigas_confinamiento_pct</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '21') and ${dano_vigas_confinamiento} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en vigas de confinamiento</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>De cada 10 vigas de confinamiento de ese piso, ¿cuántos tienen ese daño? 3 de cada 10 = 30</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>select_one niveles_dano</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>dano_entrepisos</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60')</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
+      <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr">
+        <is>
+          <t>Daño en entrepisos</t>
+        </is>
+      </c>
+      <c r="L83" t="inlineStr"/>
+      <c r="M83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>integer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>dano_entrepisos_pct</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>(${sistema_estructural} = '11' or ${sistema_estructural} = '12' or ${sistema_estructural} = '13' or ${sistema_estructural} = '14' or ${sistema_estructural} = '31' or ${sistema_estructural} = '32' or ${sistema_estructural} = '33' or ${sistema_estructural} = '41' or ${sistema_estructural} = '42' or ${sistema_estructural} = '21' or ${sistema_estructural} = '22' or ${sistema_estructural} = '23' or ${sistema_estructural} = '51' or ${sistema_estructural} = '52' or ${sistema_estructural} = '50' or ${sistema_estructural} = '60') and ${dano_entrepisos} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>. &gt;= 1 and . &lt;= 100</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr">
+        <is>
+          <t>% de extensión del daño en entrepisos</t>
+        </is>
+      </c>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>De cada 10 entrepisos de ese piso, ¿cuántos tienen ese daño? 3 de cada 10 = 30</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Debe estar entre 1 y 100</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>decimal</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>ancho_grieta_mm</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>. &gt;= 0 and . &lt;= 500</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr"/>
+      <c r="H85" t="inlineStr"/>
+      <c r="I85" t="inlineStr"/>
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr">
+        <is>
+          <t>Ancho de la peor grieta (mm), si pudo medirlo</t>
+        </is>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>Solo si tiene regla o fisurómetro. Si no, déjelo vacío y asegure la foto con un objeto de referencia.</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>Valor en milímetros</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>select_multiple senales</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>senales_alarma</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>not(selected(., 'ninguna') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr"/>
+      <c r="H86" t="inlineStr"/>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>Señales de alarma observadas</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>Marcar todas las que apliquen; si no hay, marcar «Ninguna»</t>
+        </is>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>«Ninguna» no puede combinarse con otras señales</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr"/>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
+      <c r="K87" t="inlineStr"/>
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>cierre</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
+      <c r="I88" t="inlineStr"/>
+      <c r="J88" t="inlineStr"/>
+      <c r="K88" t="inlineStr">
+        <is>
+          <t>Balance general</t>
+        </is>
+      </c>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>select_one danos_globales</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>dano_global</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>${colapso} != 'total' or . = '100'</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr"/>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>Porcentaje global de daño de la edificación</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>Área afectada frente al área total, contando daños estructurales y no estructurales. No cuente muebles ni enseres.</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Si el colapso es total, el daño global es 100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>select_multiple peligros_exterior</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>peligros_exterior</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>not(selected(., 'ninguno') and count-selected(.) &gt; 1)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr"/>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>Peligros sobre la calle, vecinos u ocupantes</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>Marcar todos los que apliquen; si no hay, «Ninguno»</t>
+        </is>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>«Ninguno» no puede combinarse con otros</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>comentarios</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr"/>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>multiline</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr"/>
+      <c r="H91" t="inlineStr"/>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>Comentarios</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>Todo lo que no cupo en el formulario: combinación de sistemas constructivos, doble nomenclatura, daños que no encajan en las preguntas, acceso, etc.</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr"/>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>begin_group</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>fotos</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>field-list</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>Fotografías</t>
+        </is>
+      </c>
+      <c r="L93" t="inlineStr"/>
+      <c r="M93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>note</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>nota_fotos</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr"/>
+      <c r="I94" t="inlineStr"/>
+      <c r="J94" t="inlineStr"/>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>Las fotos son lo más importante del reporte: el ingeniero evalúa con ellas. Tómelas con buena luz y sin personas en el encuadre.</t>
+        </is>
+      </c>
+      <c r="L94" t="inlineStr"/>
+      <c r="M94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>foto_fachada</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>Foto: fachada completa</t>
+        </is>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>Desde el frente, que se vea todo el edificio</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>foto_esquina_1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>Foto: esquina 1</t>
+        </is>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>Desde una esquina, que se vean dos fachadas a la vez</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>foto_esquina_2</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr"/>
+      <c r="J97" t="inlineStr"/>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>Foto: esquina 2</t>
+        </is>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>La esquina opuesta, si puede dar la vuelta</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>foto_esquina_3</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>Foto: esquina 3 (si es accesible)</t>
+        </is>
+      </c>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>foto_esquina_4</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>Foto: esquina 4 (si es accesible)</t>
+        </is>
+      </c>
+      <c r="L99" t="inlineStr"/>
+      <c r="M99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>foto_grieta</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada' and ${dano_global} != 'ninguno'</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>max-pixels=2048</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Foto: peor grieta, de cerca</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>Poner una moneda o una regla junto a la grieta como referencia de escala</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>image</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>foto_columnas</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>${tipo_inspeccion} != 'no_inspeccionada'</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>max-pixels=1600</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Foto: columnas o muros del primer piso</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>El primer piso es el que más carga: fotografíe sus columnas o muros aunque se vean sanos</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>end_group</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2795,7 +3895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C86"/>
+  <dimension ref="A1:C113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3151,7 +4251,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Concreto: pórtico</t>
+          <t>Concreto: pórtico (esqueleto de columnas y vigas)</t>
         </is>
       </c>
     </row>
@@ -3168,7 +4268,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Concreto: muros estructurales</t>
+          <t>Concreto: muros estructurales (muros de concreto cargan)</t>
         </is>
       </c>
     </row>
@@ -3219,7 +4319,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mampostería confinada (con vigas y columnas de amarre)</t>
+          <t>Mampostería confinada (ladrillo con vigas y columnas de amarre)</t>
         </is>
       </c>
     </row>
@@ -3236,7 +4336,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Mampostería reforzada</t>
+          <t>Mampostería reforzada (bloques con refuerzo interno)</t>
         </is>
       </c>
     </row>
@@ -3253,7 +4353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Mampostería no reforzada (sin amarres)</t>
+          <t>Mampostería no reforzada (ladrillo sin amarres)</t>
         </is>
       </c>
     </row>
@@ -3270,7 +4370,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Acero: pórticos arriostrados</t>
+          <t>Acero: pórticos arriostrados (con diagonales)</t>
         </is>
       </c>
     </row>
@@ -3355,7 +4455,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Muros en bahareque</t>
+          <t>Muros en bahareque (guadua/esterilla con revoque)</t>
         </is>
       </c>
     </row>
@@ -3372,7 +4472,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Muros en tapia</t>
+          <t>Muros en tapia (tierra pisada) o adobe</t>
         </is>
       </c>
     </row>
@@ -3389,7 +4489,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Mixta</t>
+          <t>Mixta (combinación de sistemas)</t>
         </is>
       </c>
     </row>
@@ -3746,7 +4846,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Estacionamientos</t>
+          <t>Parqueaderos</t>
         </is>
       </c>
     </row>
@@ -3838,17 +4938,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>colapsos</t>
+          <t>rangos_ano</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>total</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Colapso total</t>
+          <t>No se sabe</t>
         </is>
       </c>
     </row>
@@ -3860,12 +4960,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>parcial_mayor_50</t>
+          <t>total</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Colapso parcial (50% o más)</t>
+          <t>Colapso total</t>
         </is>
       </c>
     </row>
@@ -3877,12 +4977,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>parcial_menor_50</t>
+          <t>parcial_mayor_50</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Colapso parcial (menos del 50%)</t>
+          <t>Colapso parcial (50% o más)</t>
         </is>
       </c>
     </row>
@@ -3894,29 +4994,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>ninguno</t>
+          <t>parcial_menor_50</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Colapso parcial (menos del 50%)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>inclinaciones</t>
+          <t>colapsos</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>evidente</t>
+          <t>ninguno</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Inclinación evidente</t>
+          <t>Ninguno</t>
         </is>
       </c>
     </row>
@@ -3928,12 +5028,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>dudas</t>
+          <t>evidente</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hay dudas</t>
+          <t>Inclinación evidente</t>
         </is>
       </c>
     </row>
@@ -3945,318 +5045,777 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>ninguna</t>
+          <t>dudas</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Ninguna</t>
+          <t>Hay dudas</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>inclinaciones</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>ninguno</t>
+          <t>ninguna</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Ninguno / muy leve</t>
+          <t>Ninguna</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>asentamientos</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>leve</t>
+          <t>evidente</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Leve</t>
+          <t>Evidente</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>asentamientos</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>moderado</t>
+          <t>dudas</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Existen dudas</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>asentamientos</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>fuerte</t>
+          <t>ninguno</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Fuerte</t>
+          <t>Ninguno</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>niveles_dano</t>
+          <t>fallas_talud</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>severo</t>
+          <t>general</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Severo</t>
+          <t>General (toda la ladera o varias edificaciones)</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>fallas_talud</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ninguno</t>
+          <t>puntual</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Puntual</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>fallas_talud</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>0_10</t>
+          <t>ninguna</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>0 – 10 %</t>
+          <t>Ninguna</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>morfologias</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>10_30</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>10 – 30 %</t>
+          <t>Divisoria</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>morfologias</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>30_60</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>30 – 60 %</t>
+          <t>Cresta</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>morfologias</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>60_100</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>60 – 100 %</t>
+          <t>Ladera</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>danos_globales</t>
+          <t>morfologias</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>100 % (colapso)</t>
+          <t>Pie de ladera</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>morfologias</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>grietas_x</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Grietas en X en muros</t>
+          <t>Valle</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>morfologias</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>grietas_horizontales_base</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Grietas horizontales en base de columnas</t>
+          <t>Canal</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>morfologias</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>refuerzo_expuesto</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Refuerzo (varillas) expuesto</t>
+          <t>Borde de río</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>morfologias</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>pisos_desnivelados</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Pisos desnivelados o inclinados</t>
+          <t>Talud</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>habitada_opts</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>separacion_muro_estructura</t>
+          <t>si</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Separación entre muros y estructura</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>senales</t>
+          <t>habitada_opts</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>grieta_ancha</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Grieta llamativamente ancha (fotografiar con escala)</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
+          <t>habitada_opts</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>no_se_sabe</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>No se sabe</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>niveles_dano</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Ninguno / muy leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>niveles_dano</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>leve</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Leve</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>niveles_dano</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>moderado</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Moderado</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>niveles_dano</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>fuerte</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Fuerte</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>niveles_dano</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>severo</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Severo</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>0_10</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>0 – 10 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>10_30</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>10 – 30 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>30_60</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>30 – 60 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>60_100</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>60 – 100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>danos_globales</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>100 % (colapso)</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
           <t>senales</t>
         </is>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>grietas_x</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Grietas en X en muros</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>grietas_horizontales_base</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Grietas horizontales en base de columnas</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>refuerzo_expuesto</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Refuerzo (varillas) expuesto</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>pisos_desnivelados</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Pisos desnivelados o inclinados</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>separacion_muro_estructura</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Separación entre muros y estructura</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>grieta_ancha</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Grieta llamativamente ancha (fotografiar con escala)</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>senales</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
         <is>
           <t>ninguna</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>Ninguna</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>peligros_exterior</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>fachada_balcon</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Fachada, balcón o antepecho a punto de caer</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>peligros_exterior</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>cubierta_tejas</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Tejas o elementos de cubierta sueltos</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>peligros_exterior</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>cielo_raso</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Cielos rasos desprendidos</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>peligros_exterior</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>tanque_elevado</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Tanque elevado inclinado o suelto</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>peligros_exterior</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>gas</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Olor o fuga de gas</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>peligros_exterior</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>electricas</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Cables o postes eléctricos caídos</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>peligros_exterior</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>quimicos</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Derrame de químicos o tóxicos</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>peligros_exterior</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>escombros_via</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Escombros sobre la vía</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>peligros_exterior</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>ninguno</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Ninguno</t>
         </is>
       </c>
     </row>
@@ -4271,7 +5830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:E2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4295,11 +5854,16 @@
           <t>default_language</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>style</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SafeTag — Formulario Único AIS (v1)</t>
+          <t>SafeTag — Formulario Único AIS (v2)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -4309,12 +5873,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026081701</t>
+          <t>2026081702</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Español (es)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>pages</t>
         </is>
       </c>
     </row>
